--- a/進捗管理表/進捗管理表_森数.xlsx
+++ b/進捗管理表/進捗管理表_森数.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sensh\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sensh\Documents\mytask\MyTaskSystem\進捗管理表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{56C0AE26-0D4D-4676-9D59-F4C88A63E8CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E98A3F1-994F-4394-9BB5-9A0CA80DE6CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -323,7 +323,7 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -357,6 +357,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -890,7 +896,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1029,44 +1035,26 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1102,6 +1090,30 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1413,142 +1425,142 @@
       <c r="AL2" s="2"/>
     </row>
     <row r="3" spans="1:38" ht="13.5" customHeight="1">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="65" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="52" t="s">
+      <c r="B3" s="67" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="62">
+      <c r="G3" s="56">
         <v>45705</v>
       </c>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="63"/>
-      <c r="K3" s="63"/>
-      <c r="L3" s="63"/>
-      <c r="M3" s="63"/>
-      <c r="N3" s="63"/>
-      <c r="O3" s="63"/>
-      <c r="P3" s="63"/>
-      <c r="Q3" s="63"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="63"/>
-      <c r="T3" s="63"/>
-      <c r="U3" s="63"/>
-      <c r="V3" s="63"/>
-      <c r="W3" s="63"/>
-      <c r="X3" s="63"/>
-      <c r="Y3" s="63"/>
-      <c r="Z3" s="63"/>
-      <c r="AA3" s="63"/>
-      <c r="AB3" s="63"/>
-      <c r="AC3" s="63"/>
-      <c r="AD3" s="63"/>
-      <c r="AE3" s="63"/>
-      <c r="AF3" s="63"/>
-      <c r="AG3" s="63"/>
-      <c r="AH3" s="63"/>
-      <c r="AI3" s="63"/>
-      <c r="AJ3" s="63"/>
-      <c r="AK3" s="63"/>
-      <c r="AL3" s="64"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="57"/>
+      <c r="L3" s="57"/>
+      <c r="M3" s="57"/>
+      <c r="N3" s="57"/>
+      <c r="O3" s="57"/>
+      <c r="P3" s="57"/>
+      <c r="Q3" s="57"/>
+      <c r="R3" s="57"/>
+      <c r="S3" s="57"/>
+      <c r="T3" s="57"/>
+      <c r="U3" s="57"/>
+      <c r="V3" s="57"/>
+      <c r="W3" s="57"/>
+      <c r="X3" s="57"/>
+      <c r="Y3" s="57"/>
+      <c r="Z3" s="57"/>
+      <c r="AA3" s="57"/>
+      <c r="AB3" s="57"/>
+      <c r="AC3" s="57"/>
+      <c r="AD3" s="57"/>
+      <c r="AE3" s="57"/>
+      <c r="AF3" s="57"/>
+      <c r="AG3" s="57"/>
+      <c r="AH3" s="57"/>
+      <c r="AI3" s="57"/>
+      <c r="AJ3" s="57"/>
+      <c r="AK3" s="57"/>
+      <c r="AL3" s="58"/>
     </row>
     <row r="4" spans="1:38" ht="13.5" customHeight="1">
-      <c r="A4" s="51"/>
-      <c r="B4" s="51"/>
-      <c r="C4" s="53" t="s">
+      <c r="A4" s="66"/>
+      <c r="B4" s="66"/>
+      <c r="C4" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="50" t="s">
+      <c r="D4" s="65" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="56" t="s">
+      <c r="E4" s="70" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="59" t="s">
+      <c r="F4" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="65"/>
-      <c r="H4" s="66"/>
-      <c r="I4" s="66"/>
-      <c r="J4" s="66"/>
-      <c r="K4" s="66"/>
-      <c r="L4" s="66"/>
-      <c r="M4" s="66"/>
-      <c r="N4" s="66"/>
-      <c r="O4" s="66"/>
-      <c r="P4" s="66"/>
-      <c r="Q4" s="66"/>
-      <c r="R4" s="66"/>
-      <c r="S4" s="66"/>
-      <c r="T4" s="66"/>
-      <c r="U4" s="66"/>
-      <c r="V4" s="66"/>
-      <c r="W4" s="66"/>
-      <c r="X4" s="66"/>
-      <c r="Y4" s="66"/>
-      <c r="Z4" s="66"/>
-      <c r="AA4" s="66"/>
-      <c r="AB4" s="66"/>
-      <c r="AC4" s="66"/>
-      <c r="AD4" s="66"/>
-      <c r="AE4" s="66"/>
-      <c r="AF4" s="66"/>
-      <c r="AG4" s="66"/>
-      <c r="AH4" s="66"/>
-      <c r="AI4" s="66"/>
-      <c r="AJ4" s="66"/>
-      <c r="AK4" s="66"/>
-      <c r="AL4" s="67"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="60"/>
+      <c r="K4" s="60"/>
+      <c r="L4" s="60"/>
+      <c r="M4" s="60"/>
+      <c r="N4" s="60"/>
+      <c r="O4" s="60"/>
+      <c r="P4" s="60"/>
+      <c r="Q4" s="60"/>
+      <c r="R4" s="60"/>
+      <c r="S4" s="60"/>
+      <c r="T4" s="60"/>
+      <c r="U4" s="60"/>
+      <c r="V4" s="60"/>
+      <c r="W4" s="60"/>
+      <c r="X4" s="60"/>
+      <c r="Y4" s="60"/>
+      <c r="Z4" s="60"/>
+      <c r="AA4" s="60"/>
+      <c r="AB4" s="60"/>
+      <c r="AC4" s="60"/>
+      <c r="AD4" s="60"/>
+      <c r="AE4" s="60"/>
+      <c r="AF4" s="60"/>
+      <c r="AG4" s="60"/>
+      <c r="AH4" s="60"/>
+      <c r="AI4" s="60"/>
+      <c r="AJ4" s="60"/>
+      <c r="AK4" s="60"/>
+      <c r="AL4" s="61"/>
     </row>
     <row r="5" spans="1:38" ht="13.5" customHeight="1">
-      <c r="A5" s="51"/>
-      <c r="B5" s="51"/>
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="57">
+      <c r="A5" s="66"/>
+      <c r="B5" s="66"/>
+      <c r="C5" s="66"/>
+      <c r="D5" s="66"/>
+      <c r="E5" s="66"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="50">
         <v>17</v>
       </c>
-      <c r="H5" s="58"/>
-      <c r="I5" s="54">
+      <c r="H5" s="51"/>
+      <c r="I5" s="52">
         <v>18</v>
       </c>
-      <c r="J5" s="55"/>
-      <c r="K5" s="54">
+      <c r="J5" s="69"/>
+      <c r="K5" s="52">
         <v>19</v>
       </c>
-      <c r="L5" s="55"/>
-      <c r="M5" s="54">
+      <c r="L5" s="69"/>
+      <c r="M5" s="52">
         <v>20</v>
       </c>
-      <c r="N5" s="55"/>
-      <c r="O5" s="54">
+      <c r="N5" s="69"/>
+      <c r="O5" s="52">
         <v>21</v>
       </c>
-      <c r="P5" s="55"/>
-      <c r="Q5" s="54">
+      <c r="P5" s="69"/>
+      <c r="Q5" s="52">
         <v>25</v>
       </c>
-      <c r="R5" s="55"/>
-      <c r="S5" s="57">
+      <c r="R5" s="69"/>
+      <c r="S5" s="50">
         <v>26</v>
       </c>
-      <c r="T5" s="58"/>
-      <c r="U5" s="54">
+      <c r="T5" s="51"/>
+      <c r="U5" s="52">
         <v>27</v>
       </c>
-      <c r="V5" s="58"/>
-      <c r="W5" s="54">
+      <c r="V5" s="51"/>
+      <c r="W5" s="52">
         <v>28</v>
       </c>
-      <c r="X5" s="58"/>
+      <c r="X5" s="51"/>
       <c r="Y5" s="10"/>
       <c r="Z5" s="10"/>
       <c r="AA5" s="10"/>
@@ -1570,43 +1582,43 @@
       <c r="C6" s="47"/>
       <c r="D6" s="47"/>
       <c r="E6" s="47"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="57" t="s">
+      <c r="F6" s="55"/>
+      <c r="G6" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="58"/>
-      <c r="I6" s="68" t="s">
+      <c r="H6" s="51"/>
+      <c r="I6" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="J6" s="58"/>
-      <c r="K6" s="54" t="s">
+      <c r="J6" s="51"/>
+      <c r="K6" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="L6" s="58"/>
-      <c r="M6" s="54" t="s">
+      <c r="L6" s="51"/>
+      <c r="M6" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="N6" s="58"/>
-      <c r="O6" s="54" t="s">
+      <c r="N6" s="51"/>
+      <c r="O6" s="52" t="s">
         <v>11</v>
       </c>
-      <c r="P6" s="58"/>
-      <c r="Q6" s="54" t="s">
+      <c r="P6" s="51"/>
+      <c r="Q6" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="R6" s="58"/>
-      <c r="S6" s="69" t="s">
+      <c r="R6" s="51"/>
+      <c r="S6" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="T6" s="58"/>
-      <c r="U6" s="70" t="s">
+      <c r="T6" s="51"/>
+      <c r="U6" s="64" t="s">
         <v>21</v>
       </c>
-      <c r="V6" s="58"/>
-      <c r="W6" s="70" t="s">
+      <c r="V6" s="51"/>
+      <c r="W6" s="64" t="s">
         <v>22</v>
       </c>
-      <c r="X6" s="58"/>
+      <c r="X6" s="51"/>
       <c r="Y6" s="12"/>
       <c r="Z6" s="12"/>
       <c r="AA6" s="12"/>
@@ -1665,12 +1677,12 @@
       <c r="AL7" s="20"/>
     </row>
     <row r="8" spans="1:38" ht="12" hidden="1" customHeight="1">
-      <c r="A8" s="49">
+      <c r="A8" s="46">
         <v>1</v>
       </c>
-      <c r="C8" s="46"/>
-      <c r="D8" s="46"/>
-      <c r="E8" s="46"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="48"/>
+      <c r="E8" s="48"/>
       <c r="F8" s="21" t="s">
         <v>13</v>
       </c>
@@ -1749,12 +1761,12 @@
       <c r="AL9" s="30"/>
     </row>
     <row r="10" spans="1:38" ht="12" hidden="1" customHeight="1">
-      <c r="A10" s="49">
+      <c r="A10" s="46">
         <v>2</v>
       </c>
-      <c r="C10" s="46"/>
-      <c r="D10" s="46"/>
-      <c r="E10" s="46"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="48"/>
+      <c r="E10" s="48"/>
       <c r="F10" s="31" t="s">
         <v>13</v>
       </c>
@@ -1833,12 +1845,12 @@
       <c r="AL11" s="37"/>
     </row>
     <row r="12" spans="1:38" ht="12" hidden="1" customHeight="1">
-      <c r="A12" s="49">
+      <c r="A12" s="46">
         <v>3</v>
       </c>
-      <c r="C12" s="46"/>
-      <c r="D12" s="46"/>
-      <c r="E12" s="46"/>
+      <c r="C12" s="48"/>
+      <c r="D12" s="48"/>
+      <c r="E12" s="48"/>
       <c r="F12" s="21" t="s">
         <v>13</v>
       </c>
@@ -1917,12 +1929,12 @@
       <c r="AL13" s="30"/>
     </row>
     <row r="14" spans="1:38" ht="12" hidden="1" customHeight="1">
-      <c r="A14" s="49">
+      <c r="A14" s="46">
         <v>4</v>
       </c>
-      <c r="C14" s="46"/>
-      <c r="D14" s="46"/>
-      <c r="E14" s="46"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
       <c r="F14" s="31" t="s">
         <v>13</v>
       </c>
@@ -2001,13 +2013,13 @@
       <c r="AL15" s="37"/>
     </row>
     <row r="16" spans="1:38" ht="12" hidden="1" customHeight="1">
-      <c r="A16" s="49">
+      <c r="A16" s="46">
         <v>5</v>
       </c>
-      <c r="B16" s="46"/>
-      <c r="C16" s="46"/>
-      <c r="D16" s="46"/>
-      <c r="E16" s="46"/>
+      <c r="B16" s="48"/>
+      <c r="C16" s="48"/>
+      <c r="D16" s="48"/>
+      <c r="E16" s="48"/>
       <c r="F16" s="21" t="s">
         <v>13</v>
       </c>
@@ -2087,13 +2099,13 @@
       <c r="AL17" s="41"/>
     </row>
     <row r="18" spans="1:38" ht="12" hidden="1" customHeight="1">
-      <c r="A18" s="49">
+      <c r="A18" s="46">
         <v>6</v>
       </c>
-      <c r="B18" s="46"/>
-      <c r="C18" s="46"/>
-      <c r="D18" s="46"/>
-      <c r="E18" s="46"/>
+      <c r="B18" s="48"/>
+      <c r="C18" s="48"/>
+      <c r="D18" s="48"/>
+      <c r="E18" s="48"/>
       <c r="F18" s="31" t="s">
         <v>13</v>
       </c>
@@ -2173,13 +2185,13 @@
       <c r="AL19" s="41"/>
     </row>
     <row r="20" spans="1:38" ht="12" hidden="1" customHeight="1">
-      <c r="A20" s="49">
+      <c r="A20" s="46">
         <v>7</v>
       </c>
-      <c r="B20" s="46"/>
-      <c r="C20" s="46"/>
-      <c r="D20" s="46"/>
-      <c r="E20" s="46"/>
+      <c r="B20" s="48"/>
+      <c r="C20" s="48"/>
+      <c r="D20" s="48"/>
+      <c r="E20" s="48"/>
       <c r="F20" s="31" t="s">
         <v>13</v>
       </c>
@@ -2259,13 +2271,13 @@
       <c r="AL21" s="41"/>
     </row>
     <row r="22" spans="1:38" ht="12" hidden="1" customHeight="1">
-      <c r="A22" s="49">
+      <c r="A22" s="46">
         <v>8</v>
       </c>
-      <c r="B22" s="46"/>
-      <c r="C22" s="46"/>
-      <c r="D22" s="46"/>
-      <c r="E22" s="46"/>
+      <c r="B22" s="48"/>
+      <c r="C22" s="48"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="48"/>
       <c r="F22" s="21" t="s">
         <v>13</v>
       </c>
@@ -2387,19 +2399,19 @@
       <c r="AL24" s="20"/>
     </row>
     <row r="25" spans="1:38" ht="12" customHeight="1">
-      <c r="A25" s="49">
+      <c r="A25" s="46">
         <v>1</v>
       </c>
-      <c r="B25" s="46" t="s">
+      <c r="B25" s="48" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="46">
+      <c r="C25" s="48">
         <v>0.5</v>
       </c>
-      <c r="D25" s="46" t="s">
+      <c r="D25" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="E25" s="46" t="s">
+      <c r="E25" s="48" t="s">
         <v>40</v>
       </c>
       <c r="F25" s="21" t="s">
@@ -2443,13 +2455,13 @@
       <c r="B26" s="47"/>
       <c r="C26" s="47"/>
       <c r="D26" s="47"/>
-      <c r="E26" s="48"/>
+      <c r="E26" s="49"/>
       <c r="F26" s="27" t="s">
         <v>14</v>
       </c>
       <c r="G26" s="28"/>
       <c r="H26" s="29"/>
-      <c r="I26" s="29"/>
+      <c r="I26" s="71"/>
       <c r="J26" s="29"/>
       <c r="K26" s="29"/>
       <c r="L26" s="29"/>
@@ -2481,20 +2493,20 @@
       <c r="AL26" s="30"/>
     </row>
     <row r="27" spans="1:38" ht="12" customHeight="1">
-      <c r="A27" s="49">
+      <c r="A27" s="46">
         <v>2</v>
       </c>
-      <c r="B27" s="46" t="s">
+      <c r="B27" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="46">
+      <c r="C27" s="48">
         <v>1</v>
       </c>
-      <c r="D27" s="46" t="s">
+      <c r="D27" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="E27" s="46" t="s">
-        <v>39</v>
+      <c r="E27" s="48" t="s">
+        <v>40</v>
       </c>
       <c r="F27" s="31" t="s">
         <v>13</v>
@@ -2537,13 +2549,13 @@
       <c r="B28" s="47"/>
       <c r="C28" s="47"/>
       <c r="D28" s="47"/>
-      <c r="E28" s="48"/>
+      <c r="E28" s="49"/>
       <c r="F28" s="34" t="s">
         <v>14</v>
       </c>
       <c r="G28" s="35"/>
       <c r="H28" s="36"/>
-      <c r="I28" s="36"/>
+      <c r="I28" s="72"/>
       <c r="J28" s="36"/>
       <c r="K28" s="36"/>
       <c r="L28" s="36"/>
@@ -2575,19 +2587,19 @@
       <c r="AL28" s="37"/>
     </row>
     <row r="29" spans="1:38" ht="12" customHeight="1">
-      <c r="A29" s="49">
+      <c r="A29" s="46">
         <v>3</v>
       </c>
-      <c r="B29" s="46" t="s">
+      <c r="B29" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="46">
+      <c r="C29" s="48">
         <v>1</v>
       </c>
-      <c r="D29" s="46" t="s">
+      <c r="D29" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="E29" s="46" t="s">
+      <c r="E29" s="48" t="s">
         <v>39</v>
       </c>
       <c r="F29" s="21" t="s">
@@ -2631,7 +2643,7 @@
       <c r="B30" s="47"/>
       <c r="C30" s="47"/>
       <c r="D30" s="47"/>
-      <c r="E30" s="48"/>
+      <c r="E30" s="49"/>
       <c r="F30" s="38" t="s">
         <v>14</v>
       </c>
@@ -2669,19 +2681,19 @@
       <c r="AL30" s="30"/>
     </row>
     <row r="31" spans="1:38" ht="12" customHeight="1">
-      <c r="A31" s="49">
+      <c r="A31" s="46">
         <v>4</v>
       </c>
-      <c r="B31" s="46" t="s">
+      <c r="B31" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="C31" s="46">
+      <c r="C31" s="48">
         <v>1</v>
       </c>
-      <c r="D31" s="46" t="s">
+      <c r="D31" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="E31" s="46" t="s">
+      <c r="E31" s="48" t="s">
         <v>35</v>
       </c>
       <c r="F31" s="31" t="s">
@@ -2725,7 +2737,7 @@
       <c r="B32" s="47"/>
       <c r="C32" s="47"/>
       <c r="D32" s="47"/>
-      <c r="E32" s="48"/>
+      <c r="E32" s="49"/>
       <c r="F32" s="34" t="s">
         <v>14</v>
       </c>
@@ -2763,15 +2775,15 @@
       <c r="AL32" s="37"/>
     </row>
     <row r="33" spans="1:38" ht="12" customHeight="1">
-      <c r="A33" s="49">
+      <c r="A33" s="46">
         <v>5</v>
       </c>
-      <c r="B33" s="46"/>
-      <c r="C33" s="46"/>
-      <c r="D33" s="46" t="s">
+      <c r="B33" s="48"/>
+      <c r="C33" s="48"/>
+      <c r="D33" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="E33" s="46" t="s">
+      <c r="E33" s="48" t="s">
         <v>35</v>
       </c>
       <c r="F33" s="21" t="s">
@@ -2814,7 +2826,7 @@
       <c r="B34" s="47"/>
       <c r="C34" s="47"/>
       <c r="D34" s="47"/>
-      <c r="E34" s="48"/>
+      <c r="E34" s="49"/>
       <c r="F34" s="38" t="s">
         <v>14</v>
       </c>
@@ -2852,13 +2864,13 @@
       <c r="AL34" s="41"/>
     </row>
     <row r="35" spans="1:38" ht="12" customHeight="1">
-      <c r="A35" s="49">
+      <c r="A35" s="46">
         <v>6</v>
       </c>
-      <c r="B35" s="46"/>
-      <c r="C35" s="46"/>
-      <c r="D35" s="46"/>
-      <c r="E35" s="46"/>
+      <c r="B35" s="48"/>
+      <c r="C35" s="48"/>
+      <c r="D35" s="48"/>
+      <c r="E35" s="48"/>
       <c r="F35" s="31" t="s">
         <v>13</v>
       </c>
@@ -2980,19 +2992,19 @@
       <c r="AL37" s="20"/>
     </row>
     <row r="38" spans="1:38" ht="12" customHeight="1">
-      <c r="A38" s="49">
+      <c r="A38" s="46">
         <v>1</v>
       </c>
-      <c r="B38" s="46" t="s">
+      <c r="B38" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="C38" s="46">
+      <c r="C38" s="48">
         <v>3</v>
       </c>
-      <c r="D38" s="46" t="s">
+      <c r="D38" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="E38" s="46" t="s">
+      <c r="E38" s="48" t="s">
         <v>35</v>
       </c>
       <c r="F38" s="21" t="s">
@@ -3036,7 +3048,7 @@
       <c r="B39" s="47"/>
       <c r="C39" s="47"/>
       <c r="D39" s="47"/>
-      <c r="E39" s="48"/>
+      <c r="E39" s="49"/>
       <c r="F39" s="27" t="s">
         <v>14</v>
       </c>
@@ -3074,19 +3086,19 @@
       <c r="AL39" s="30"/>
     </row>
     <row r="40" spans="1:38" ht="12" customHeight="1">
-      <c r="A40" s="49">
+      <c r="A40" s="46">
         <v>2</v>
       </c>
-      <c r="B40" s="46" t="s">
+      <c r="B40" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="C40" s="46">
+      <c r="C40" s="48">
         <v>1</v>
       </c>
-      <c r="D40" s="46" t="s">
+      <c r="D40" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="E40" s="46" t="s">
+      <c r="E40" s="48" t="s">
         <v>35</v>
       </c>
       <c r="F40" s="31" t="s">
@@ -3130,7 +3142,7 @@
       <c r="B41" s="47"/>
       <c r="C41" s="47"/>
       <c r="D41" s="47"/>
-      <c r="E41" s="48"/>
+      <c r="E41" s="49"/>
       <c r="F41" s="34" t="s">
         <v>14</v>
       </c>
@@ -3168,19 +3180,19 @@
       <c r="AL41" s="37"/>
     </row>
     <row r="42" spans="1:38" ht="12" customHeight="1">
-      <c r="A42" s="49">
+      <c r="A42" s="46">
         <v>3</v>
       </c>
-      <c r="B42" s="46" t="s">
+      <c r="B42" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="C42" s="46">
+      <c r="C42" s="48">
         <v>4</v>
       </c>
-      <c r="D42" s="46" t="s">
+      <c r="D42" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="E42" s="46" t="s">
+      <c r="E42" s="48" t="s">
         <v>35</v>
       </c>
       <c r="F42" s="21" t="s">
@@ -3221,10 +3233,10 @@
     </row>
     <row r="43" spans="1:38" ht="12" customHeight="1">
       <c r="A43" s="47"/>
-      <c r="B43" s="48"/>
+      <c r="B43" s="49"/>
       <c r="C43" s="47"/>
       <c r="D43" s="47"/>
-      <c r="E43" s="48"/>
+      <c r="E43" s="49"/>
       <c r="F43" s="38" t="s">
         <v>14</v>
       </c>
@@ -3262,19 +3274,19 @@
       <c r="AL43" s="30"/>
     </row>
     <row r="44" spans="1:38" ht="12" customHeight="1">
-      <c r="A44" s="49">
+      <c r="A44" s="46">
         <v>4</v>
       </c>
-      <c r="B44" s="46" t="s">
+      <c r="B44" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="C44" s="46">
+      <c r="C44" s="48">
         <v>2</v>
       </c>
-      <c r="D44" s="46" t="s">
+      <c r="D44" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="E44" s="46" t="s">
+      <c r="E44" s="48" t="s">
         <v>35</v>
       </c>
       <c r="F44" s="31" t="s">
@@ -3317,7 +3329,7 @@
       <c r="B45" s="47"/>
       <c r="C45" s="47"/>
       <c r="D45" s="47"/>
-      <c r="E45" s="48"/>
+      <c r="E45" s="49"/>
       <c r="F45" s="34" t="s">
         <v>14</v>
       </c>
@@ -3355,13 +3367,13 @@
       <c r="AL45" s="37"/>
     </row>
     <row r="46" spans="1:38" ht="12" customHeight="1">
-      <c r="A46" s="49">
+      <c r="A46" s="46">
         <v>5</v>
       </c>
-      <c r="B46" s="46"/>
-      <c r="C46" s="46"/>
-      <c r="D46" s="46"/>
-      <c r="E46" s="46"/>
+      <c r="B46" s="48"/>
+      <c r="C46" s="48"/>
+      <c r="D46" s="48"/>
+      <c r="E46" s="48"/>
       <c r="F46" s="21" t="s">
         <v>13</v>
       </c>
@@ -3441,13 +3453,13 @@
       <c r="AL47" s="41"/>
     </row>
     <row r="48" spans="1:38" ht="12" customHeight="1">
-      <c r="A48" s="49">
+      <c r="A48" s="46">
         <v>6</v>
       </c>
-      <c r="B48" s="46"/>
-      <c r="C48" s="46"/>
-      <c r="D48" s="46"/>
-      <c r="E48" s="46"/>
+      <c r="B48" s="48"/>
+      <c r="C48" s="48"/>
+      <c r="D48" s="48"/>
+      <c r="E48" s="48"/>
       <c r="F48" s="31" t="s">
         <v>13</v>
       </c>
@@ -3569,19 +3581,19 @@
       <c r="AL50" s="20"/>
     </row>
     <row r="51" spans="1:38" ht="12" customHeight="1">
-      <c r="A51" s="49">
+      <c r="A51" s="46">
         <v>1</v>
       </c>
-      <c r="B51" s="46" t="s">
+      <c r="B51" s="48" t="s">
         <v>31</v>
       </c>
-      <c r="C51" s="46">
+      <c r="C51" s="48">
         <v>4</v>
       </c>
-      <c r="D51" s="46" t="s">
+      <c r="D51" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="E51" s="46" t="s">
+      <c r="E51" s="48" t="s">
         <v>35</v>
       </c>
       <c r="F51" s="21" t="s">
@@ -3625,7 +3637,7 @@
       <c r="B52" s="47"/>
       <c r="C52" s="47"/>
       <c r="D52" s="47"/>
-      <c r="E52" s="48"/>
+      <c r="E52" s="49"/>
       <c r="F52" s="27" t="s">
         <v>14</v>
       </c>
@@ -3663,19 +3675,19 @@
       <c r="AL52" s="30"/>
     </row>
     <row r="53" spans="1:38" ht="12" customHeight="1">
-      <c r="A53" s="49">
+      <c r="A53" s="46">
         <v>2</v>
       </c>
-      <c r="B53" s="46" t="s">
+      <c r="B53" s="48" t="s">
         <v>32</v>
       </c>
-      <c r="C53" s="46">
+      <c r="C53" s="48">
         <v>4</v>
       </c>
-      <c r="D53" s="46" t="s">
+      <c r="D53" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="E53" s="46" t="s">
+      <c r="E53" s="48" t="s">
         <v>35</v>
       </c>
       <c r="F53" s="31" t="s">
@@ -3718,8 +3730,8 @@
       <c r="A54" s="47"/>
       <c r="B54" s="47"/>
       <c r="C54" s="47"/>
-      <c r="D54" s="48"/>
-      <c r="E54" s="48"/>
+      <c r="D54" s="49"/>
+      <c r="E54" s="49"/>
       <c r="F54" s="34" t="s">
         <v>14</v>
       </c>
@@ -3757,19 +3769,19 @@
       <c r="AL54" s="37"/>
     </row>
     <row r="55" spans="1:38" ht="12" customHeight="1">
-      <c r="A55" s="49">
+      <c r="A55" s="46">
         <v>3</v>
       </c>
-      <c r="B55" s="46" t="s">
+      <c r="B55" s="48" t="s">
         <v>33</v>
       </c>
-      <c r="C55" s="46">
+      <c r="C55" s="48">
         <v>2</v>
       </c>
-      <c r="D55" s="46" t="s">
+      <c r="D55" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="E55" s="46" t="s">
+      <c r="E55" s="48" t="s">
         <v>35</v>
       </c>
       <c r="F55" s="21" t="s">
@@ -3812,8 +3824,8 @@
       <c r="A56" s="47"/>
       <c r="B56" s="47"/>
       <c r="C56" s="47"/>
-      <c r="D56" s="48"/>
-      <c r="E56" s="48"/>
+      <c r="D56" s="49"/>
+      <c r="E56" s="49"/>
       <c r="F56" s="38" t="s">
         <v>14</v>
       </c>
@@ -3851,19 +3863,19 @@
       <c r="AL56" s="30"/>
     </row>
     <row r="57" spans="1:38" ht="12" customHeight="1">
-      <c r="A57" s="49">
+      <c r="A57" s="46">
         <v>4</v>
       </c>
-      <c r="B57" s="46" t="s">
+      <c r="B57" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="C57" s="46">
+      <c r="C57" s="48">
         <v>3</v>
       </c>
-      <c r="D57" s="46" t="s">
+      <c r="D57" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="E57" s="46" t="s">
+      <c r="E57" s="48" t="s">
         <v>35</v>
       </c>
       <c r="F57" s="31" t="s">
@@ -3906,8 +3918,8 @@
       <c r="A58" s="47"/>
       <c r="B58" s="47"/>
       <c r="C58" s="47"/>
-      <c r="D58" s="48"/>
-      <c r="E58" s="48"/>
+      <c r="D58" s="49"/>
+      <c r="E58" s="49"/>
       <c r="F58" s="34" t="s">
         <v>14</v>
       </c>
@@ -3945,13 +3957,13 @@
       <c r="AL58" s="37"/>
     </row>
     <row r="59" spans="1:38" ht="12" customHeight="1">
-      <c r="A59" s="49">
+      <c r="A59" s="46">
         <v>5</v>
       </c>
-      <c r="B59" s="46"/>
-      <c r="C59" s="46"/>
-      <c r="D59" s="46"/>
-      <c r="E59" s="46"/>
+      <c r="B59" s="48"/>
+      <c r="C59" s="48"/>
+      <c r="D59" s="48"/>
+      <c r="E59" s="48"/>
       <c r="F59" s="21" t="s">
         <v>13</v>
       </c>
@@ -4031,13 +4043,13 @@
       <c r="AL60" s="41"/>
     </row>
     <row r="61" spans="1:38" ht="12" customHeight="1">
-      <c r="A61" s="49">
+      <c r="A61" s="46">
         <v>6</v>
       </c>
-      <c r="B61" s="46"/>
-      <c r="C61" s="46"/>
-      <c r="D61" s="46"/>
-      <c r="E61" s="46"/>
+      <c r="B61" s="48"/>
+      <c r="C61" s="48"/>
+      <c r="D61" s="48"/>
+      <c r="E61" s="48"/>
       <c r="F61" s="31" t="s">
         <v>13</v>
       </c>
@@ -4159,19 +4171,19 @@
       <c r="AL63" s="20"/>
     </row>
     <row r="64" spans="1:38" ht="12" customHeight="1">
-      <c r="A64" s="49">
+      <c r="A64" s="46">
         <v>1</v>
       </c>
-      <c r="B64" s="46" t="s">
+      <c r="B64" s="48" t="s">
         <v>37</v>
       </c>
-      <c r="C64" s="46">
+      <c r="C64" s="48">
         <v>2</v>
       </c>
-      <c r="D64" s="46" t="s">
+      <c r="D64" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="E64" s="46" t="s">
+      <c r="E64" s="48" t="s">
         <v>38</v>
       </c>
       <c r="F64" s="21" t="s">
@@ -4253,13 +4265,13 @@
       <c r="AL65" s="30"/>
     </row>
     <row r="66" spans="1:38" ht="12" customHeight="1">
-      <c r="A66" s="49">
+      <c r="A66" s="46">
         <v>2</v>
       </c>
-      <c r="B66" s="46"/>
-      <c r="C66" s="46"/>
-      <c r="D66" s="46"/>
-      <c r="E66" s="46"/>
+      <c r="B66" s="48"/>
+      <c r="C66" s="48"/>
+      <c r="D66" s="48"/>
+      <c r="E66" s="48"/>
       <c r="F66" s="31" t="s">
         <v>13</v>
       </c>
@@ -4339,13 +4351,13 @@
       <c r="AL67" s="37"/>
     </row>
     <row r="68" spans="1:38" ht="12" customHeight="1">
-      <c r="A68" s="49">
+      <c r="A68" s="46">
         <v>3</v>
       </c>
-      <c r="B68" s="46"/>
-      <c r="C68" s="46"/>
-      <c r="D68" s="46"/>
-      <c r="E68" s="46"/>
+      <c r="B68" s="48"/>
+      <c r="C68" s="48"/>
+      <c r="D68" s="48"/>
+      <c r="E68" s="48"/>
       <c r="F68" s="21" t="s">
         <v>13</v>
       </c>
@@ -4425,13 +4437,13 @@
       <c r="AL69" s="30"/>
     </row>
     <row r="70" spans="1:38" ht="12" customHeight="1">
-      <c r="A70" s="49">
+      <c r="A70" s="46">
         <v>4</v>
       </c>
-      <c r="B70" s="46"/>
-      <c r="C70" s="46"/>
-      <c r="D70" s="46"/>
-      <c r="E70" s="46"/>
+      <c r="B70" s="48"/>
+      <c r="C70" s="48"/>
+      <c r="D70" s="48"/>
+      <c r="E70" s="48"/>
       <c r="F70" s="31" t="s">
         <v>13</v>
       </c>
@@ -4511,13 +4523,13 @@
       <c r="AL71" s="37"/>
     </row>
     <row r="72" spans="1:38" ht="12" customHeight="1">
-      <c r="A72" s="49">
+      <c r="A72" s="46">
         <v>5</v>
       </c>
-      <c r="B72" s="46"/>
-      <c r="C72" s="46"/>
-      <c r="D72" s="46"/>
-      <c r="E72" s="46"/>
+      <c r="B72" s="48"/>
+      <c r="C72" s="48"/>
+      <c r="D72" s="48"/>
+      <c r="E72" s="48"/>
       <c r="F72" s="21" t="s">
         <v>13</v>
       </c>
@@ -4597,13 +4609,13 @@
       <c r="AL73" s="41"/>
     </row>
     <row r="74" spans="1:38" ht="12" customHeight="1">
-      <c r="A74" s="49">
+      <c r="A74" s="46">
         <v>6</v>
       </c>
-      <c r="B74" s="46"/>
-      <c r="C74" s="46"/>
-      <c r="D74" s="46"/>
-      <c r="E74" s="46"/>
+      <c r="B74" s="48"/>
+      <c r="C74" s="48"/>
+      <c r="D74" s="48"/>
+      <c r="E74" s="48"/>
       <c r="F74" s="31" t="s">
         <v>13</v>
       </c>
@@ -4723,13 +4735,13 @@
       <c r="AL76" s="20"/>
     </row>
     <row r="77" spans="1:38" ht="12" customHeight="1">
-      <c r="A77" s="49">
+      <c r="A77" s="46">
         <v>1</v>
       </c>
-      <c r="B77" s="46"/>
-      <c r="C77" s="46"/>
-      <c r="D77" s="46"/>
-      <c r="E77" s="46"/>
+      <c r="B77" s="48"/>
+      <c r="C77" s="48"/>
+      <c r="D77" s="48"/>
+      <c r="E77" s="48"/>
       <c r="F77" s="21" t="s">
         <v>13</v>
       </c>
@@ -4809,13 +4821,13 @@
       <c r="AL78" s="30"/>
     </row>
     <row r="79" spans="1:38" ht="12" customHeight="1">
-      <c r="A79" s="49">
+      <c r="A79" s="46">
         <v>2</v>
       </c>
-      <c r="B79" s="46"/>
-      <c r="C79" s="46"/>
-      <c r="D79" s="46"/>
-      <c r="E79" s="46"/>
+      <c r="B79" s="48"/>
+      <c r="C79" s="48"/>
+      <c r="D79" s="48"/>
+      <c r="E79" s="48"/>
       <c r="F79" s="31" t="s">
         <v>13</v>
       </c>
@@ -4895,13 +4907,13 @@
       <c r="AL80" s="37"/>
     </row>
     <row r="81" spans="1:38" ht="12" customHeight="1">
-      <c r="A81" s="49">
+      <c r="A81" s="46">
         <v>3</v>
       </c>
-      <c r="B81" s="46"/>
-      <c r="C81" s="46"/>
-      <c r="D81" s="46"/>
-      <c r="E81" s="46"/>
+      <c r="B81" s="48"/>
+      <c r="C81" s="48"/>
+      <c r="D81" s="48"/>
+      <c r="E81" s="48"/>
       <c r="F81" s="21" t="s">
         <v>13</v>
       </c>
@@ -4981,13 +4993,13 @@
       <c r="AL82" s="30"/>
     </row>
     <row r="83" spans="1:38" ht="12" customHeight="1">
-      <c r="A83" s="49">
+      <c r="A83" s="46">
         <v>4</v>
       </c>
-      <c r="B83" s="46"/>
-      <c r="C83" s="46"/>
-      <c r="D83" s="46"/>
-      <c r="E83" s="46"/>
+      <c r="B83" s="48"/>
+      <c r="C83" s="48"/>
+      <c r="D83" s="48"/>
+      <c r="E83" s="48"/>
       <c r="F83" s="31" t="s">
         <v>13</v>
       </c>
@@ -41708,16 +41720,173 @@
     </row>
   </sheetData>
   <mergeCells count="201">
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="E46:E47"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="D48:D49"/>
-    <mergeCell ref="E48:E49"/>
-    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="C57:C58"/>
+    <mergeCell ref="D57:D58"/>
+    <mergeCell ref="E57:E58"/>
+    <mergeCell ref="A59:A60"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="D66:D67"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="D64:D65"/>
+    <mergeCell ref="E64:E65"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="E66:E67"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="D55:D56"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="C53:C54"/>
+    <mergeCell ref="D53:D54"/>
+    <mergeCell ref="E53:E54"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="E55:E56"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="E42:E43"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="E44:E45"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="D4:D6"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="O5:P5"/>
+    <mergeCell ref="Q5:R5"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="S5:T5"/>
+    <mergeCell ref="U5:V5"/>
+    <mergeCell ref="W5:X5"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="F4:F6"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G3:AL4"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="O6:P6"/>
+    <mergeCell ref="Q6:R6"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="U6:V6"/>
+    <mergeCell ref="W6:X6"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="E33:E34"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="E35:E36"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="A77:A78"/>
+    <mergeCell ref="B77:B78"/>
+    <mergeCell ref="C77:C78"/>
+    <mergeCell ref="D77:D78"/>
+    <mergeCell ref="E77:E78"/>
+    <mergeCell ref="C81:C82"/>
+    <mergeCell ref="D81:D82"/>
+    <mergeCell ref="A81:A82"/>
+    <mergeCell ref="A83:A84"/>
+    <mergeCell ref="B83:B84"/>
+    <mergeCell ref="C83:C84"/>
+    <mergeCell ref="D83:D84"/>
+    <mergeCell ref="E83:E84"/>
+    <mergeCell ref="A79:A80"/>
+    <mergeCell ref="B79:B80"/>
+    <mergeCell ref="C79:C80"/>
+    <mergeCell ref="D79:D80"/>
+    <mergeCell ref="E79:E80"/>
+    <mergeCell ref="B81:B82"/>
+    <mergeCell ref="E81:E82"/>
+    <mergeCell ref="D74:D75"/>
+    <mergeCell ref="E74:E75"/>
+    <mergeCell ref="A70:A71"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="E72:E73"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="C74:C75"/>
     <mergeCell ref="A51:A52"/>
     <mergeCell ref="B51:B52"/>
     <mergeCell ref="C51:C52"/>
@@ -41742,173 +41911,16 @@
     <mergeCell ref="D59:D60"/>
     <mergeCell ref="E59:E60"/>
     <mergeCell ref="A57:A58"/>
-    <mergeCell ref="D74:D75"/>
-    <mergeCell ref="E74:E75"/>
-    <mergeCell ref="A70:A71"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="D72:D73"/>
-    <mergeCell ref="E72:E73"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="C74:C75"/>
-    <mergeCell ref="A77:A78"/>
-    <mergeCell ref="B77:B78"/>
-    <mergeCell ref="C77:C78"/>
-    <mergeCell ref="D77:D78"/>
-    <mergeCell ref="E77:E78"/>
-    <mergeCell ref="C81:C82"/>
-    <mergeCell ref="D81:D82"/>
-    <mergeCell ref="A81:A82"/>
-    <mergeCell ref="A83:A84"/>
-    <mergeCell ref="B83:B84"/>
-    <mergeCell ref="C83:C84"/>
-    <mergeCell ref="D83:D84"/>
-    <mergeCell ref="E83:E84"/>
-    <mergeCell ref="A79:A80"/>
-    <mergeCell ref="B79:B80"/>
-    <mergeCell ref="C79:C80"/>
-    <mergeCell ref="D79:D80"/>
-    <mergeCell ref="E79:E80"/>
-    <mergeCell ref="B81:B82"/>
-    <mergeCell ref="E81:E82"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="E33:E34"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="E35:E36"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="S5:T5"/>
-    <mergeCell ref="U5:V5"/>
-    <mergeCell ref="W5:X5"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="F4:F6"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G3:AL4"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="O6:P6"/>
-    <mergeCell ref="Q6:R6"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="U6:V6"/>
-    <mergeCell ref="W6:X6"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="B3:B6"/>
-    <mergeCell ref="C4:C6"/>
-    <mergeCell ref="D4:D6"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="O5:P5"/>
-    <mergeCell ref="Q5:R5"/>
-    <mergeCell ref="E4:E6"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="E27:E28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="E31:E32"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="D55:D56"/>
-    <mergeCell ref="A53:A54"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="C53:C54"/>
-    <mergeCell ref="D53:D54"/>
-    <mergeCell ref="E53:E54"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="E55:E56"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="E40:E41"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="E42:E43"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="E44:E45"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="B57:B58"/>
-    <mergeCell ref="C57:C58"/>
-    <mergeCell ref="D57:D58"/>
-    <mergeCell ref="E57:E58"/>
-    <mergeCell ref="A59:A60"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="D66:D67"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="C64:C65"/>
-    <mergeCell ref="D64:D65"/>
-    <mergeCell ref="E64:E65"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="E66:E67"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="E46:E47"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="E48:E49"/>
+    <mergeCell ref="B46:B47"/>
   </mergeCells>
   <phoneticPr fontId="7"/>
   <dataValidations count="1">

--- a/進捗管理表/進捗管理表_森数.xlsx
+++ b/進捗管理表/進捗管理表_森数.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sensh\Documents\mytask\MyTaskSystem\進捗管理表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E98A3F1-994F-4394-9BB5-9A0CA80DE6CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D15DB9BC-E3DE-4D47-B607-DFB375B99ACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="42">
   <si>
     <t>■進捗管理表</t>
   </si>
@@ -250,6 +250,9 @@
   <si>
     <t>作成完了</t>
   </si>
+  <si>
+    <t>レビュー完了</t>
+  </si>
 </sst>
 </file>
 
@@ -287,6 +290,8 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
@@ -896,7 +901,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1035,26 +1040,50 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1092,28 +1121,7 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1425,142 +1433,142 @@
       <c r="AL2" s="2"/>
     </row>
     <row r="3" spans="1:38" ht="13.5" customHeight="1">
-      <c r="A3" s="65" t="s">
+      <c r="A3" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="67" t="s">
+      <c r="B3" s="54" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="56">
+      <c r="G3" s="64">
         <v>45705</v>
       </c>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="57"/>
-      <c r="L3" s="57"/>
-      <c r="M3" s="57"/>
-      <c r="N3" s="57"/>
-      <c r="O3" s="57"/>
-      <c r="P3" s="57"/>
-      <c r="Q3" s="57"/>
-      <c r="R3" s="57"/>
-      <c r="S3" s="57"/>
-      <c r="T3" s="57"/>
-      <c r="U3" s="57"/>
-      <c r="V3" s="57"/>
-      <c r="W3" s="57"/>
-      <c r="X3" s="57"/>
-      <c r="Y3" s="57"/>
-      <c r="Z3" s="57"/>
-      <c r="AA3" s="57"/>
-      <c r="AB3" s="57"/>
-      <c r="AC3" s="57"/>
-      <c r="AD3" s="57"/>
-      <c r="AE3" s="57"/>
-      <c r="AF3" s="57"/>
-      <c r="AG3" s="57"/>
-      <c r="AH3" s="57"/>
-      <c r="AI3" s="57"/>
-      <c r="AJ3" s="57"/>
-      <c r="AK3" s="57"/>
-      <c r="AL3" s="58"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="65"/>
+      <c r="K3" s="65"/>
+      <c r="L3" s="65"/>
+      <c r="M3" s="65"/>
+      <c r="N3" s="65"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="65"/>
+      <c r="U3" s="65"/>
+      <c r="V3" s="65"/>
+      <c r="W3" s="65"/>
+      <c r="X3" s="65"/>
+      <c r="Y3" s="65"/>
+      <c r="Z3" s="65"/>
+      <c r="AA3" s="65"/>
+      <c r="AB3" s="65"/>
+      <c r="AC3" s="65"/>
+      <c r="AD3" s="65"/>
+      <c r="AE3" s="65"/>
+      <c r="AF3" s="65"/>
+      <c r="AG3" s="65"/>
+      <c r="AH3" s="65"/>
+      <c r="AI3" s="65"/>
+      <c r="AJ3" s="65"/>
+      <c r="AK3" s="65"/>
+      <c r="AL3" s="66"/>
     </row>
     <row r="4" spans="1:38" ht="13.5" customHeight="1">
-      <c r="A4" s="66"/>
-      <c r="B4" s="66"/>
-      <c r="C4" s="68" t="s">
+      <c r="A4" s="53"/>
+      <c r="B4" s="53"/>
+      <c r="C4" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="65" t="s">
+      <c r="D4" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="70" t="s">
+      <c r="E4" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="53" t="s">
+      <c r="F4" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="59"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="60"/>
-      <c r="L4" s="60"/>
-      <c r="M4" s="60"/>
-      <c r="N4" s="60"/>
-      <c r="O4" s="60"/>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="60"/>
-      <c r="U4" s="60"/>
-      <c r="V4" s="60"/>
-      <c r="W4" s="60"/>
-      <c r="X4" s="60"/>
-      <c r="Y4" s="60"/>
-      <c r="Z4" s="60"/>
-      <c r="AA4" s="60"/>
-      <c r="AB4" s="60"/>
-      <c r="AC4" s="60"/>
-      <c r="AD4" s="60"/>
-      <c r="AE4" s="60"/>
-      <c r="AF4" s="60"/>
-      <c r="AG4" s="60"/>
-      <c r="AH4" s="60"/>
-      <c r="AI4" s="60"/>
-      <c r="AJ4" s="60"/>
-      <c r="AK4" s="60"/>
-      <c r="AL4" s="61"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="68"/>
+      <c r="K4" s="68"/>
+      <c r="L4" s="68"/>
+      <c r="M4" s="68"/>
+      <c r="N4" s="68"/>
+      <c r="O4" s="68"/>
+      <c r="P4" s="68"/>
+      <c r="Q4" s="68"/>
+      <c r="R4" s="68"/>
+      <c r="S4" s="68"/>
+      <c r="T4" s="68"/>
+      <c r="U4" s="68"/>
+      <c r="V4" s="68"/>
+      <c r="W4" s="68"/>
+      <c r="X4" s="68"/>
+      <c r="Y4" s="68"/>
+      <c r="Z4" s="68"/>
+      <c r="AA4" s="68"/>
+      <c r="AB4" s="68"/>
+      <c r="AC4" s="68"/>
+      <c r="AD4" s="68"/>
+      <c r="AE4" s="68"/>
+      <c r="AF4" s="68"/>
+      <c r="AG4" s="68"/>
+      <c r="AH4" s="68"/>
+      <c r="AI4" s="68"/>
+      <c r="AJ4" s="68"/>
+      <c r="AK4" s="68"/>
+      <c r="AL4" s="69"/>
     </row>
     <row r="5" spans="1:38" ht="13.5" customHeight="1">
-      <c r="A5" s="66"/>
-      <c r="B5" s="66"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="50">
+      <c r="A5" s="53"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="53"/>
+      <c r="E5" s="53"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="59">
         <v>17</v>
       </c>
-      <c r="H5" s="51"/>
-      <c r="I5" s="52">
+      <c r="H5" s="60"/>
+      <c r="I5" s="56">
         <v>18</v>
       </c>
-      <c r="J5" s="69"/>
-      <c r="K5" s="52">
+      <c r="J5" s="57"/>
+      <c r="K5" s="56">
         <v>19</v>
       </c>
-      <c r="L5" s="69"/>
-      <c r="M5" s="52">
+      <c r="L5" s="57"/>
+      <c r="M5" s="56">
         <v>20</v>
       </c>
-      <c r="N5" s="69"/>
-      <c r="O5" s="52">
+      <c r="N5" s="57"/>
+      <c r="O5" s="56">
         <v>21</v>
       </c>
-      <c r="P5" s="69"/>
-      <c r="Q5" s="52">
+      <c r="P5" s="57"/>
+      <c r="Q5" s="56">
         <v>25</v>
       </c>
-      <c r="R5" s="69"/>
-      <c r="S5" s="50">
+      <c r="R5" s="57"/>
+      <c r="S5" s="59">
         <v>26</v>
       </c>
-      <c r="T5" s="51"/>
-      <c r="U5" s="52">
+      <c r="T5" s="60"/>
+      <c r="U5" s="56">
         <v>27</v>
       </c>
-      <c r="V5" s="51"/>
-      <c r="W5" s="52">
+      <c r="V5" s="60"/>
+      <c r="W5" s="56">
         <v>28</v>
       </c>
-      <c r="X5" s="51"/>
+      <c r="X5" s="60"/>
       <c r="Y5" s="10"/>
       <c r="Z5" s="10"/>
       <c r="AA5" s="10"/>
@@ -1577,48 +1585,48 @@
       <c r="AL5" s="11"/>
     </row>
     <row r="6" spans="1:38" ht="13.5" customHeight="1">
-      <c r="A6" s="47"/>
-      <c r="B6" s="47"/>
-      <c r="C6" s="47"/>
-      <c r="D6" s="47"/>
-      <c r="E6" s="47"/>
-      <c r="F6" s="55"/>
-      <c r="G6" s="50" t="s">
+      <c r="A6" s="49"/>
+      <c r="B6" s="49"/>
+      <c r="C6" s="49"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="49"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="51"/>
-      <c r="I6" s="62" t="s">
+      <c r="H6" s="60"/>
+      <c r="I6" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="J6" s="51"/>
-      <c r="K6" s="52" t="s">
+      <c r="J6" s="60"/>
+      <c r="K6" s="56" t="s">
         <v>9</v>
       </c>
-      <c r="L6" s="51"/>
-      <c r="M6" s="52" t="s">
+      <c r="L6" s="60"/>
+      <c r="M6" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="N6" s="51"/>
-      <c r="O6" s="52" t="s">
+      <c r="N6" s="60"/>
+      <c r="O6" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="P6" s="51"/>
-      <c r="Q6" s="52" t="s">
+      <c r="P6" s="60"/>
+      <c r="Q6" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="R6" s="51"/>
-      <c r="S6" s="63" t="s">
+      <c r="R6" s="60"/>
+      <c r="S6" s="71" t="s">
         <v>20</v>
       </c>
-      <c r="T6" s="51"/>
-      <c r="U6" s="64" t="s">
+      <c r="T6" s="60"/>
+      <c r="U6" s="72" t="s">
         <v>21</v>
       </c>
-      <c r="V6" s="51"/>
-      <c r="W6" s="64" t="s">
+      <c r="V6" s="60"/>
+      <c r="W6" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="X6" s="51"/>
+      <c r="X6" s="60"/>
       <c r="Y6" s="12"/>
       <c r="Z6" s="12"/>
       <c r="AA6" s="12"/>
@@ -1677,7 +1685,7 @@
       <c r="AL7" s="20"/>
     </row>
     <row r="8" spans="1:38" ht="12" hidden="1" customHeight="1">
-      <c r="A8" s="46">
+      <c r="A8" s="51">
         <v>1</v>
       </c>
       <c r="C8" s="48"/>
@@ -1720,10 +1728,10 @@
       <c r="AL8" s="26"/>
     </row>
     <row r="9" spans="1:38" ht="12" hidden="1" customHeight="1">
-      <c r="A9" s="47"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="47"/>
-      <c r="E9" s="47"/>
+      <c r="A9" s="49"/>
+      <c r="C9" s="49"/>
+      <c r="D9" s="49"/>
+      <c r="E9" s="49"/>
       <c r="F9" s="27" t="s">
         <v>14</v>
       </c>
@@ -1761,7 +1769,7 @@
       <c r="AL9" s="30"/>
     </row>
     <row r="10" spans="1:38" ht="12" hidden="1" customHeight="1">
-      <c r="A10" s="46">
+      <c r="A10" s="51">
         <v>2</v>
       </c>
       <c r="C10" s="48"/>
@@ -1804,10 +1812,10 @@
       <c r="AL10" s="10"/>
     </row>
     <row r="11" spans="1:38" ht="12" hidden="1" customHeight="1">
-      <c r="A11" s="47"/>
-      <c r="C11" s="47"/>
-      <c r="D11" s="47"/>
-      <c r="E11" s="47"/>
+      <c r="A11" s="49"/>
+      <c r="C11" s="49"/>
+      <c r="D11" s="49"/>
+      <c r="E11" s="49"/>
       <c r="F11" s="34" t="s">
         <v>14</v>
       </c>
@@ -1845,7 +1853,7 @@
       <c r="AL11" s="37"/>
     </row>
     <row r="12" spans="1:38" ht="12" hidden="1" customHeight="1">
-      <c r="A12" s="46">
+      <c r="A12" s="51">
         <v>3</v>
       </c>
       <c r="C12" s="48"/>
@@ -1888,10 +1896,10 @@
       <c r="AL12" s="26"/>
     </row>
     <row r="13" spans="1:38" ht="12" hidden="1" customHeight="1">
-      <c r="A13" s="47"/>
-      <c r="C13" s="47"/>
-      <c r="D13" s="47"/>
-      <c r="E13" s="47"/>
+      <c r="A13" s="49"/>
+      <c r="C13" s="49"/>
+      <c r="D13" s="49"/>
+      <c r="E13" s="49"/>
       <c r="F13" s="38" t="s">
         <v>14</v>
       </c>
@@ -1929,7 +1937,7 @@
       <c r="AL13" s="30"/>
     </row>
     <row r="14" spans="1:38" ht="12" hidden="1" customHeight="1">
-      <c r="A14" s="46">
+      <c r="A14" s="51">
         <v>4</v>
       </c>
       <c r="C14" s="48"/>
@@ -1972,10 +1980,10 @@
       <c r="AL14" s="10"/>
     </row>
     <row r="15" spans="1:38" ht="12" hidden="1" customHeight="1">
-      <c r="A15" s="47"/>
-      <c r="C15" s="47"/>
-      <c r="D15" s="47"/>
-      <c r="E15" s="47"/>
+      <c r="A15" s="49"/>
+      <c r="C15" s="49"/>
+      <c r="D15" s="49"/>
+      <c r="E15" s="49"/>
       <c r="F15" s="34" t="s">
         <v>14</v>
       </c>
@@ -2013,7 +2021,7 @@
       <c r="AL15" s="37"/>
     </row>
     <row r="16" spans="1:38" ht="12" hidden="1" customHeight="1">
-      <c r="A16" s="46">
+      <c r="A16" s="51">
         <v>5</v>
       </c>
       <c r="B16" s="48"/>
@@ -2057,11 +2065,11 @@
       <c r="AL16" s="26"/>
     </row>
     <row r="17" spans="1:38" ht="12" hidden="1" customHeight="1">
-      <c r="A17" s="47"/>
-      <c r="B17" s="47"/>
-      <c r="C17" s="47"/>
-      <c r="D17" s="47"/>
-      <c r="E17" s="47"/>
+      <c r="A17" s="49"/>
+      <c r="B17" s="49"/>
+      <c r="C17" s="49"/>
+      <c r="D17" s="49"/>
+      <c r="E17" s="49"/>
       <c r="F17" s="38" t="s">
         <v>14</v>
       </c>
@@ -2099,7 +2107,7 @@
       <c r="AL17" s="41"/>
     </row>
     <row r="18" spans="1:38" ht="12" hidden="1" customHeight="1">
-      <c r="A18" s="46">
+      <c r="A18" s="51">
         <v>6</v>
       </c>
       <c r="B18" s="48"/>
@@ -2143,11 +2151,11 @@
       <c r="AL18" s="10"/>
     </row>
     <row r="19" spans="1:38" ht="12" hidden="1" customHeight="1">
-      <c r="A19" s="47"/>
-      <c r="B19" s="47"/>
-      <c r="C19" s="47"/>
-      <c r="D19" s="47"/>
-      <c r="E19" s="47"/>
+      <c r="A19" s="49"/>
+      <c r="B19" s="49"/>
+      <c r="C19" s="49"/>
+      <c r="D19" s="49"/>
+      <c r="E19" s="49"/>
       <c r="F19" s="27" t="s">
         <v>14</v>
       </c>
@@ -2185,7 +2193,7 @@
       <c r="AL19" s="41"/>
     </row>
     <row r="20" spans="1:38" ht="12" hidden="1" customHeight="1">
-      <c r="A20" s="46">
+      <c r="A20" s="51">
         <v>7</v>
       </c>
       <c r="B20" s="48"/>
@@ -2229,11 +2237,11 @@
       <c r="AL20" s="10"/>
     </row>
     <row r="21" spans="1:38" ht="12" hidden="1" customHeight="1">
-      <c r="A21" s="47"/>
-      <c r="B21" s="47"/>
-      <c r="C21" s="47"/>
-      <c r="D21" s="47"/>
-      <c r="E21" s="47"/>
+      <c r="A21" s="49"/>
+      <c r="B21" s="49"/>
+      <c r="C21" s="49"/>
+      <c r="D21" s="49"/>
+      <c r="E21" s="49"/>
       <c r="F21" s="27" t="s">
         <v>14</v>
       </c>
@@ -2271,7 +2279,7 @@
       <c r="AL21" s="41"/>
     </row>
     <row r="22" spans="1:38" ht="12" hidden="1" customHeight="1">
-      <c r="A22" s="46">
+      <c r="A22" s="51">
         <v>8</v>
       </c>
       <c r="B22" s="48"/>
@@ -2315,11 +2323,11 @@
       <c r="AL22" s="26"/>
     </row>
     <row r="23" spans="1:38" ht="12" hidden="1" customHeight="1">
-      <c r="A23" s="47"/>
-      <c r="B23" s="47"/>
-      <c r="C23" s="47"/>
-      <c r="D23" s="47"/>
-      <c r="E23" s="47"/>
+      <c r="A23" s="49"/>
+      <c r="B23" s="49"/>
+      <c r="C23" s="49"/>
+      <c r="D23" s="49"/>
+      <c r="E23" s="49"/>
       <c r="F23" s="34" t="s">
         <v>14</v>
       </c>
@@ -2399,7 +2407,7 @@
       <c r="AL24" s="20"/>
     </row>
     <row r="25" spans="1:38" ht="12" customHeight="1">
-      <c r="A25" s="46">
+      <c r="A25" s="51">
         <v>1</v>
       </c>
       <c r="B25" s="48" t="s">
@@ -2451,17 +2459,17 @@
       <c r="AL25" s="26"/>
     </row>
     <row r="26" spans="1:38" ht="12" customHeight="1">
-      <c r="A26" s="47"/>
-      <c r="B26" s="47"/>
-      <c r="C26" s="47"/>
-      <c r="D26" s="47"/>
-      <c r="E26" s="49"/>
+      <c r="A26" s="49"/>
+      <c r="B26" s="49"/>
+      <c r="C26" s="49"/>
+      <c r="D26" s="49"/>
+      <c r="E26" s="50"/>
       <c r="F26" s="27" t="s">
         <v>14</v>
       </c>
       <c r="G26" s="28"/>
       <c r="H26" s="29"/>
-      <c r="I26" s="71"/>
+      <c r="I26" s="46"/>
       <c r="J26" s="29"/>
       <c r="K26" s="29"/>
       <c r="L26" s="29"/>
@@ -2493,7 +2501,7 @@
       <c r="AL26" s="30"/>
     </row>
     <row r="27" spans="1:38" ht="12" customHeight="1">
-      <c r="A27" s="46">
+      <c r="A27" s="51">
         <v>2</v>
       </c>
       <c r="B27" s="48" t="s">
@@ -2545,17 +2553,17 @@
       <c r="AL27" s="10"/>
     </row>
     <row r="28" spans="1:38" ht="12" customHeight="1">
-      <c r="A28" s="47"/>
-      <c r="B28" s="47"/>
-      <c r="C28" s="47"/>
-      <c r="D28" s="47"/>
-      <c r="E28" s="49"/>
+      <c r="A28" s="49"/>
+      <c r="B28" s="49"/>
+      <c r="C28" s="49"/>
+      <c r="D28" s="49"/>
+      <c r="E28" s="50"/>
       <c r="F28" s="34" t="s">
         <v>14</v>
       </c>
       <c r="G28" s="35"/>
       <c r="H28" s="36"/>
-      <c r="I28" s="72"/>
+      <c r="I28" s="47"/>
       <c r="J28" s="36"/>
       <c r="K28" s="36"/>
       <c r="L28" s="36"/>
@@ -2587,7 +2595,7 @@
       <c r="AL28" s="37"/>
     </row>
     <row r="29" spans="1:38" ht="12" customHeight="1">
-      <c r="A29" s="46">
+      <c r="A29" s="51">
         <v>3</v>
       </c>
       <c r="B29" s="48" t="s">
@@ -2600,7 +2608,7 @@
         <v>26</v>
       </c>
       <c r="E29" s="48" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F29" s="21" t="s">
         <v>13</v>
@@ -2639,18 +2647,18 @@
       <c r="AL29" s="26"/>
     </row>
     <row r="30" spans="1:38" ht="12" customHeight="1">
-      <c r="A30" s="47"/>
-      <c r="B30" s="47"/>
-      <c r="C30" s="47"/>
-      <c r="D30" s="47"/>
-      <c r="E30" s="49"/>
+      <c r="A30" s="49"/>
+      <c r="B30" s="49"/>
+      <c r="C30" s="49"/>
+      <c r="D30" s="49"/>
+      <c r="E30" s="50"/>
       <c r="F30" s="38" t="s">
         <v>14</v>
       </c>
       <c r="G30" s="39"/>
       <c r="H30" s="40"/>
       <c r="I30" s="40"/>
-      <c r="J30" s="40"/>
+      <c r="J30" s="73"/>
       <c r="K30" s="40"/>
       <c r="L30" s="40"/>
       <c r="M30" s="40"/>
@@ -2681,7 +2689,7 @@
       <c r="AL30" s="30"/>
     </row>
     <row r="31" spans="1:38" ht="12" customHeight="1">
-      <c r="A31" s="46">
+      <c r="A31" s="51">
         <v>4</v>
       </c>
       <c r="B31" s="48" t="s">
@@ -2694,7 +2702,7 @@
         <v>26</v>
       </c>
       <c r="E31" s="48" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F31" s="31" t="s">
         <v>13</v>
@@ -2733,11 +2741,11 @@
       <c r="AL31" s="10"/>
     </row>
     <row r="32" spans="1:38" ht="12" customHeight="1">
-      <c r="A32" s="47"/>
-      <c r="B32" s="47"/>
-      <c r="C32" s="47"/>
-      <c r="D32" s="47"/>
-      <c r="E32" s="49"/>
+      <c r="A32" s="49"/>
+      <c r="B32" s="49"/>
+      <c r="C32" s="49"/>
+      <c r="D32" s="49"/>
+      <c r="E32" s="50"/>
       <c r="F32" s="34" t="s">
         <v>14</v>
       </c>
@@ -2746,7 +2754,7 @@
       <c r="I32" s="23"/>
       <c r="J32" s="36"/>
       <c r="K32" s="36"/>
-      <c r="L32" s="36"/>
+      <c r="L32" s="47"/>
       <c r="M32" s="36"/>
       <c r="N32" s="36"/>
       <c r="O32" s="36"/>
@@ -2775,17 +2783,13 @@
       <c r="AL32" s="37"/>
     </row>
     <row r="33" spans="1:38" ht="12" customHeight="1">
-      <c r="A33" s="46">
+      <c r="A33" s="51">
         <v>5</v>
       </c>
       <c r="B33" s="48"/>
       <c r="C33" s="48"/>
-      <c r="D33" s="48" t="s">
-        <v>26</v>
-      </c>
-      <c r="E33" s="48" t="s">
-        <v>35</v>
-      </c>
+      <c r="D33" s="48"/>
+      <c r="E33" s="48"/>
       <c r="F33" s="21" t="s">
         <v>13</v>
       </c>
@@ -2822,11 +2826,11 @@
       <c r="AL33" s="26"/>
     </row>
     <row r="34" spans="1:38" ht="12" customHeight="1">
-      <c r="A34" s="47"/>
-      <c r="B34" s="47"/>
-      <c r="C34" s="47"/>
-      <c r="D34" s="47"/>
-      <c r="E34" s="49"/>
+      <c r="A34" s="49"/>
+      <c r="B34" s="49"/>
+      <c r="C34" s="49"/>
+      <c r="D34" s="49"/>
+      <c r="E34" s="50"/>
       <c r="F34" s="38" t="s">
         <v>14</v>
       </c>
@@ -2864,7 +2868,7 @@
       <c r="AL34" s="41"/>
     </row>
     <row r="35" spans="1:38" ht="12" customHeight="1">
-      <c r="A35" s="46">
+      <c r="A35" s="51">
         <v>6</v>
       </c>
       <c r="B35" s="48"/>
@@ -2908,11 +2912,11 @@
       <c r="AL35" s="10"/>
     </row>
     <row r="36" spans="1:38" ht="12" customHeight="1">
-      <c r="A36" s="47"/>
-      <c r="B36" s="47"/>
-      <c r="C36" s="47"/>
-      <c r="D36" s="47"/>
-      <c r="E36" s="47"/>
+      <c r="A36" s="49"/>
+      <c r="B36" s="49"/>
+      <c r="C36" s="49"/>
+      <c r="D36" s="49"/>
+      <c r="E36" s="49"/>
       <c r="F36" s="34" t="s">
         <v>14</v>
       </c>
@@ -2992,7 +2996,7 @@
       <c r="AL37" s="20"/>
     </row>
     <row r="38" spans="1:38" ht="12" customHeight="1">
-      <c r="A38" s="46">
+      <c r="A38" s="51">
         <v>1</v>
       </c>
       <c r="B38" s="48" t="s">
@@ -3005,7 +3009,7 @@
         <v>26</v>
       </c>
       <c r="E38" s="48" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F38" s="21" t="s">
         <v>13</v>
@@ -3044,11 +3048,11 @@
       <c r="AL38" s="26"/>
     </row>
     <row r="39" spans="1:38" ht="12" customHeight="1">
-      <c r="A39" s="47"/>
-      <c r="B39" s="47"/>
-      <c r="C39" s="47"/>
-      <c r="D39" s="47"/>
-      <c r="E39" s="49"/>
+      <c r="A39" s="49"/>
+      <c r="B39" s="49"/>
+      <c r="C39" s="49"/>
+      <c r="D39" s="49"/>
+      <c r="E39" s="50"/>
       <c r="F39" s="27" t="s">
         <v>14</v>
       </c>
@@ -3086,7 +3090,7 @@
       <c r="AL39" s="30"/>
     </row>
     <row r="40" spans="1:38" ht="12" customHeight="1">
-      <c r="A40" s="46">
+      <c r="A40" s="51">
         <v>2</v>
       </c>
       <c r="B40" s="48" t="s">
@@ -3099,7 +3103,7 @@
         <v>26</v>
       </c>
       <c r="E40" s="48" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F40" s="31" t="s">
         <v>13</v>
@@ -3138,11 +3142,11 @@
       <c r="AL40" s="10"/>
     </row>
     <row r="41" spans="1:38" ht="12" customHeight="1">
-      <c r="A41" s="47"/>
-      <c r="B41" s="47"/>
-      <c r="C41" s="47"/>
-      <c r="D41" s="47"/>
-      <c r="E41" s="49"/>
+      <c r="A41" s="49"/>
+      <c r="B41" s="49"/>
+      <c r="C41" s="49"/>
+      <c r="D41" s="49"/>
+      <c r="E41" s="50"/>
       <c r="F41" s="34" t="s">
         <v>14</v>
       </c>
@@ -3180,7 +3184,7 @@
       <c r="AL41" s="37"/>
     </row>
     <row r="42" spans="1:38" ht="12" customHeight="1">
-      <c r="A42" s="46">
+      <c r="A42" s="51">
         <v>3</v>
       </c>
       <c r="B42" s="48" t="s">
@@ -3232,11 +3236,11 @@
       <c r="AL42" s="26"/>
     </row>
     <row r="43" spans="1:38" ht="12" customHeight="1">
-      <c r="A43" s="47"/>
-      <c r="B43" s="49"/>
-      <c r="C43" s="47"/>
-      <c r="D43" s="47"/>
-      <c r="E43" s="49"/>
+      <c r="A43" s="49"/>
+      <c r="B43" s="50"/>
+      <c r="C43" s="49"/>
+      <c r="D43" s="49"/>
+      <c r="E43" s="50"/>
       <c r="F43" s="38" t="s">
         <v>14</v>
       </c>
@@ -3274,7 +3278,7 @@
       <c r="AL43" s="30"/>
     </row>
     <row r="44" spans="1:38" ht="12" customHeight="1">
-      <c r="A44" s="46">
+      <c r="A44" s="51">
         <v>4</v>
       </c>
       <c r="B44" s="48" t="s">
@@ -3325,11 +3329,11 @@
       <c r="AL44" s="10"/>
     </row>
     <row r="45" spans="1:38" ht="12" customHeight="1">
-      <c r="A45" s="47"/>
-      <c r="B45" s="47"/>
-      <c r="C45" s="47"/>
-      <c r="D45" s="47"/>
-      <c r="E45" s="49"/>
+      <c r="A45" s="49"/>
+      <c r="B45" s="49"/>
+      <c r="C45" s="49"/>
+      <c r="D45" s="49"/>
+      <c r="E45" s="50"/>
       <c r="F45" s="34" t="s">
         <v>14</v>
       </c>
@@ -3367,7 +3371,7 @@
       <c r="AL45" s="37"/>
     </row>
     <row r="46" spans="1:38" ht="12" customHeight="1">
-      <c r="A46" s="46">
+      <c r="A46" s="51">
         <v>5</v>
       </c>
       <c r="B46" s="48"/>
@@ -3411,11 +3415,11 @@
       <c r="AL46" s="26"/>
     </row>
     <row r="47" spans="1:38" ht="12" customHeight="1">
-      <c r="A47" s="47"/>
-      <c r="B47" s="47"/>
-      <c r="C47" s="47"/>
-      <c r="D47" s="47"/>
-      <c r="E47" s="47"/>
+      <c r="A47" s="49"/>
+      <c r="B47" s="49"/>
+      <c r="C47" s="49"/>
+      <c r="D47" s="49"/>
+      <c r="E47" s="49"/>
       <c r="F47" s="38" t="s">
         <v>14</v>
       </c>
@@ -3453,7 +3457,7 @@
       <c r="AL47" s="41"/>
     </row>
     <row r="48" spans="1:38" ht="12" customHeight="1">
-      <c r="A48" s="46">
+      <c r="A48" s="51">
         <v>6</v>
       </c>
       <c r="B48" s="48"/>
@@ -3497,11 +3501,11 @@
       <c r="AL48" s="10"/>
     </row>
     <row r="49" spans="1:38" ht="12" customHeight="1">
-      <c r="A49" s="47"/>
-      <c r="B49" s="47"/>
-      <c r="C49" s="47"/>
-      <c r="D49" s="47"/>
-      <c r="E49" s="47"/>
+      <c r="A49" s="49"/>
+      <c r="B49" s="49"/>
+      <c r="C49" s="49"/>
+      <c r="D49" s="49"/>
+      <c r="E49" s="49"/>
       <c r="F49" s="34" t="s">
         <v>14</v>
       </c>
@@ -3581,7 +3585,7 @@
       <c r="AL50" s="20"/>
     </row>
     <row r="51" spans="1:38" ht="12" customHeight="1">
-      <c r="A51" s="46">
+      <c r="A51" s="51">
         <v>1</v>
       </c>
       <c r="B51" s="48" t="s">
@@ -3633,11 +3637,11 @@
       <c r="AL51" s="26"/>
     </row>
     <row r="52" spans="1:38" ht="12" customHeight="1">
-      <c r="A52" s="47"/>
-      <c r="B52" s="47"/>
-      <c r="C52" s="47"/>
-      <c r="D52" s="47"/>
-      <c r="E52" s="49"/>
+      <c r="A52" s="49"/>
+      <c r="B52" s="49"/>
+      <c r="C52" s="49"/>
+      <c r="D52" s="49"/>
+      <c r="E52" s="50"/>
       <c r="F52" s="27" t="s">
         <v>14</v>
       </c>
@@ -3675,7 +3679,7 @@
       <c r="AL52" s="30"/>
     </row>
     <row r="53" spans="1:38" ht="12" customHeight="1">
-      <c r="A53" s="46">
+      <c r="A53" s="51">
         <v>2</v>
       </c>
       <c r="B53" s="48" t="s">
@@ -3727,11 +3731,11 @@
       <c r="AL53" s="10"/>
     </row>
     <row r="54" spans="1:38" ht="12" customHeight="1">
-      <c r="A54" s="47"/>
-      <c r="B54" s="47"/>
-      <c r="C54" s="47"/>
-      <c r="D54" s="49"/>
-      <c r="E54" s="49"/>
+      <c r="A54" s="49"/>
+      <c r="B54" s="49"/>
+      <c r="C54" s="49"/>
+      <c r="D54" s="50"/>
+      <c r="E54" s="50"/>
       <c r="F54" s="34" t="s">
         <v>14</v>
       </c>
@@ -3769,7 +3773,7 @@
       <c r="AL54" s="37"/>
     </row>
     <row r="55" spans="1:38" ht="12" customHeight="1">
-      <c r="A55" s="46">
+      <c r="A55" s="51">
         <v>3</v>
       </c>
       <c r="B55" s="48" t="s">
@@ -3821,11 +3825,11 @@
       <c r="AL55" s="26"/>
     </row>
     <row r="56" spans="1:38" ht="12" customHeight="1">
-      <c r="A56" s="47"/>
-      <c r="B56" s="47"/>
-      <c r="C56" s="47"/>
-      <c r="D56" s="49"/>
-      <c r="E56" s="49"/>
+      <c r="A56" s="49"/>
+      <c r="B56" s="49"/>
+      <c r="C56" s="49"/>
+      <c r="D56" s="50"/>
+      <c r="E56" s="50"/>
       <c r="F56" s="38" t="s">
         <v>14</v>
       </c>
@@ -3863,7 +3867,7 @@
       <c r="AL56" s="30"/>
     </row>
     <row r="57" spans="1:38" ht="12" customHeight="1">
-      <c r="A57" s="46">
+      <c r="A57" s="51">
         <v>4</v>
       </c>
       <c r="B57" s="48" t="s">
@@ -3915,11 +3919,11 @@
       <c r="AL57" s="10"/>
     </row>
     <row r="58" spans="1:38" ht="12" customHeight="1">
-      <c r="A58" s="47"/>
-      <c r="B58" s="47"/>
-      <c r="C58" s="47"/>
-      <c r="D58" s="49"/>
-      <c r="E58" s="49"/>
+      <c r="A58" s="49"/>
+      <c r="B58" s="49"/>
+      <c r="C58" s="49"/>
+      <c r="D58" s="50"/>
+      <c r="E58" s="50"/>
       <c r="F58" s="34" t="s">
         <v>14</v>
       </c>
@@ -3957,7 +3961,7 @@
       <c r="AL58" s="37"/>
     </row>
     <row r="59" spans="1:38" ht="12" customHeight="1">
-      <c r="A59" s="46">
+      <c r="A59" s="51">
         <v>5</v>
       </c>
       <c r="B59" s="48"/>
@@ -4001,11 +4005,11 @@
       <c r="AL59" s="26"/>
     </row>
     <row r="60" spans="1:38" ht="12" customHeight="1">
-      <c r="A60" s="47"/>
-      <c r="B60" s="47"/>
-      <c r="C60" s="47"/>
-      <c r="D60" s="47"/>
-      <c r="E60" s="47"/>
+      <c r="A60" s="49"/>
+      <c r="B60" s="49"/>
+      <c r="C60" s="49"/>
+      <c r="D60" s="49"/>
+      <c r="E60" s="49"/>
       <c r="F60" s="38" t="s">
         <v>14</v>
       </c>
@@ -4043,7 +4047,7 @@
       <c r="AL60" s="41"/>
     </row>
     <row r="61" spans="1:38" ht="12" customHeight="1">
-      <c r="A61" s="46">
+      <c r="A61" s="51">
         <v>6</v>
       </c>
       <c r="B61" s="48"/>
@@ -4087,11 +4091,11 @@
       <c r="AL61" s="10"/>
     </row>
     <row r="62" spans="1:38" ht="12" customHeight="1">
-      <c r="A62" s="47"/>
-      <c r="B62" s="47"/>
-      <c r="C62" s="47"/>
-      <c r="D62" s="47"/>
-      <c r="E62" s="47"/>
+      <c r="A62" s="49"/>
+      <c r="B62" s="49"/>
+      <c r="C62" s="49"/>
+      <c r="D62" s="49"/>
+      <c r="E62" s="49"/>
       <c r="F62" s="34" t="s">
         <v>14</v>
       </c>
@@ -4171,7 +4175,7 @@
       <c r="AL63" s="20"/>
     </row>
     <row r="64" spans="1:38" ht="12" customHeight="1">
-      <c r="A64" s="46">
+      <c r="A64" s="51">
         <v>1</v>
       </c>
       <c r="B64" s="48" t="s">
@@ -4223,11 +4227,11 @@
       <c r="AL64" s="26"/>
     </row>
     <row r="65" spans="1:38" ht="12" customHeight="1">
-      <c r="A65" s="47"/>
-      <c r="B65" s="47"/>
-      <c r="C65" s="47"/>
-      <c r="D65" s="47"/>
-      <c r="E65" s="47"/>
+      <c r="A65" s="49"/>
+      <c r="B65" s="49"/>
+      <c r="C65" s="49"/>
+      <c r="D65" s="49"/>
+      <c r="E65" s="49"/>
       <c r="F65" s="27" t="s">
         <v>14</v>
       </c>
@@ -4265,7 +4269,7 @@
       <c r="AL65" s="30"/>
     </row>
     <row r="66" spans="1:38" ht="12" customHeight="1">
-      <c r="A66" s="46">
+      <c r="A66" s="51">
         <v>2</v>
       </c>
       <c r="B66" s="48"/>
@@ -4309,11 +4313,11 @@
       <c r="AL66" s="10"/>
     </row>
     <row r="67" spans="1:38" ht="12" customHeight="1">
-      <c r="A67" s="47"/>
-      <c r="B67" s="47"/>
-      <c r="C67" s="47"/>
-      <c r="D67" s="47"/>
-      <c r="E67" s="47"/>
+      <c r="A67" s="49"/>
+      <c r="B67" s="49"/>
+      <c r="C67" s="49"/>
+      <c r="D67" s="49"/>
+      <c r="E67" s="49"/>
       <c r="F67" s="34" t="s">
         <v>14</v>
       </c>
@@ -4351,7 +4355,7 @@
       <c r="AL67" s="37"/>
     </row>
     <row r="68" spans="1:38" ht="12" customHeight="1">
-      <c r="A68" s="46">
+      <c r="A68" s="51">
         <v>3</v>
       </c>
       <c r="B68" s="48"/>
@@ -4395,11 +4399,11 @@
       <c r="AL68" s="26"/>
     </row>
     <row r="69" spans="1:38" ht="12" customHeight="1">
-      <c r="A69" s="47"/>
-      <c r="B69" s="47"/>
-      <c r="C69" s="47"/>
-      <c r="D69" s="47"/>
-      <c r="E69" s="47"/>
+      <c r="A69" s="49"/>
+      <c r="B69" s="49"/>
+      <c r="C69" s="49"/>
+      <c r="D69" s="49"/>
+      <c r="E69" s="49"/>
       <c r="F69" s="38" t="s">
         <v>14</v>
       </c>
@@ -4437,7 +4441,7 @@
       <c r="AL69" s="30"/>
     </row>
     <row r="70" spans="1:38" ht="12" customHeight="1">
-      <c r="A70" s="46">
+      <c r="A70" s="51">
         <v>4</v>
       </c>
       <c r="B70" s="48"/>
@@ -4481,11 +4485,11 @@
       <c r="AL70" s="10"/>
     </row>
     <row r="71" spans="1:38" ht="12" customHeight="1">
-      <c r="A71" s="47"/>
-      <c r="B71" s="47"/>
-      <c r="C71" s="47"/>
-      <c r="D71" s="47"/>
-      <c r="E71" s="47"/>
+      <c r="A71" s="49"/>
+      <c r="B71" s="49"/>
+      <c r="C71" s="49"/>
+      <c r="D71" s="49"/>
+      <c r="E71" s="49"/>
       <c r="F71" s="34" t="s">
         <v>14</v>
       </c>
@@ -4523,7 +4527,7 @@
       <c r="AL71" s="37"/>
     </row>
     <row r="72" spans="1:38" ht="12" customHeight="1">
-      <c r="A72" s="46">
+      <c r="A72" s="51">
         <v>5</v>
       </c>
       <c r="B72" s="48"/>
@@ -4567,11 +4571,11 @@
       <c r="AL72" s="26"/>
     </row>
     <row r="73" spans="1:38" ht="12" customHeight="1">
-      <c r="A73" s="47"/>
-      <c r="B73" s="47"/>
-      <c r="C73" s="47"/>
-      <c r="D73" s="47"/>
-      <c r="E73" s="47"/>
+      <c r="A73" s="49"/>
+      <c r="B73" s="49"/>
+      <c r="C73" s="49"/>
+      <c r="D73" s="49"/>
+      <c r="E73" s="49"/>
       <c r="F73" s="38" t="s">
         <v>14</v>
       </c>
@@ -4609,7 +4613,7 @@
       <c r="AL73" s="41"/>
     </row>
     <row r="74" spans="1:38" ht="12" customHeight="1">
-      <c r="A74" s="46">
+      <c r="A74" s="51">
         <v>6</v>
       </c>
       <c r="B74" s="48"/>
@@ -4653,11 +4657,11 @@
       <c r="AL74" s="10"/>
     </row>
     <row r="75" spans="1:38" ht="12" customHeight="1">
-      <c r="A75" s="47"/>
-      <c r="B75" s="47"/>
-      <c r="C75" s="47"/>
-      <c r="D75" s="47"/>
-      <c r="E75" s="47"/>
+      <c r="A75" s="49"/>
+      <c r="B75" s="49"/>
+      <c r="C75" s="49"/>
+      <c r="D75" s="49"/>
+      <c r="E75" s="49"/>
       <c r="F75" s="34" t="s">
         <v>14</v>
       </c>
@@ -4735,7 +4739,7 @@
       <c r="AL76" s="20"/>
     </row>
     <row r="77" spans="1:38" ht="12" customHeight="1">
-      <c r="A77" s="46">
+      <c r="A77" s="51">
         <v>1</v>
       </c>
       <c r="B77" s="48"/>
@@ -4779,11 +4783,11 @@
       <c r="AL77" s="26"/>
     </row>
     <row r="78" spans="1:38" ht="12" customHeight="1">
-      <c r="A78" s="47"/>
-      <c r="B78" s="47"/>
-      <c r="C78" s="47"/>
-      <c r="D78" s="47"/>
-      <c r="E78" s="47"/>
+      <c r="A78" s="49"/>
+      <c r="B78" s="49"/>
+      <c r="C78" s="49"/>
+      <c r="D78" s="49"/>
+      <c r="E78" s="49"/>
       <c r="F78" s="27" t="s">
         <v>14</v>
       </c>
@@ -4821,7 +4825,7 @@
       <c r="AL78" s="30"/>
     </row>
     <row r="79" spans="1:38" ht="12" customHeight="1">
-      <c r="A79" s="46">
+      <c r="A79" s="51">
         <v>2</v>
       </c>
       <c r="B79" s="48"/>
@@ -4865,11 +4869,11 @@
       <c r="AL79" s="10"/>
     </row>
     <row r="80" spans="1:38" ht="12" customHeight="1">
-      <c r="A80" s="47"/>
-      <c r="B80" s="47"/>
-      <c r="C80" s="47"/>
-      <c r="D80" s="47"/>
-      <c r="E80" s="47"/>
+      <c r="A80" s="49"/>
+      <c r="B80" s="49"/>
+      <c r="C80" s="49"/>
+      <c r="D80" s="49"/>
+      <c r="E80" s="49"/>
       <c r="F80" s="34" t="s">
         <v>14</v>
       </c>
@@ -4907,7 +4911,7 @@
       <c r="AL80" s="37"/>
     </row>
     <row r="81" spans="1:38" ht="12" customHeight="1">
-      <c r="A81" s="46">
+      <c r="A81" s="51">
         <v>3</v>
       </c>
       <c r="B81" s="48"/>
@@ -4951,11 +4955,11 @@
       <c r="AL81" s="26"/>
     </row>
     <row r="82" spans="1:38" ht="12" customHeight="1">
-      <c r="A82" s="47"/>
-      <c r="B82" s="47"/>
-      <c r="C82" s="47"/>
-      <c r="D82" s="47"/>
-      <c r="E82" s="47"/>
+      <c r="A82" s="49"/>
+      <c r="B82" s="49"/>
+      <c r="C82" s="49"/>
+      <c r="D82" s="49"/>
+      <c r="E82" s="49"/>
       <c r="F82" s="38" t="s">
         <v>14</v>
       </c>
@@ -4993,7 +4997,7 @@
       <c r="AL82" s="30"/>
     </row>
     <row r="83" spans="1:38" ht="12" customHeight="1">
-      <c r="A83" s="46">
+      <c r="A83" s="51">
         <v>4</v>
       </c>
       <c r="B83" s="48"/>
@@ -5037,11 +5041,11 @@
       <c r="AL83" s="10"/>
     </row>
     <row r="84" spans="1:38" ht="12" customHeight="1">
-      <c r="A84" s="47"/>
-      <c r="B84" s="47"/>
-      <c r="C84" s="47"/>
-      <c r="D84" s="47"/>
-      <c r="E84" s="47"/>
+      <c r="A84" s="49"/>
+      <c r="B84" s="49"/>
+      <c r="C84" s="49"/>
+      <c r="D84" s="49"/>
+      <c r="E84" s="49"/>
       <c r="F84" s="38" t="s">
         <v>14</v>
       </c>
@@ -41720,21 +41724,168 @@
     </row>
   </sheetData>
   <mergeCells count="201">
-    <mergeCell ref="B57:B58"/>
-    <mergeCell ref="C57:C58"/>
-    <mergeCell ref="D57:D58"/>
-    <mergeCell ref="E57:E58"/>
-    <mergeCell ref="A59:A60"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="D66:D67"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="C64:C65"/>
-    <mergeCell ref="D64:D65"/>
-    <mergeCell ref="E64:E65"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="E66:E67"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="E46:E47"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="E48:E49"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="C51:C52"/>
+    <mergeCell ref="D51:D52"/>
+    <mergeCell ref="E51:E52"/>
+    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="D70:D71"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="D68:D69"/>
+    <mergeCell ref="E68:E69"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="E70:E71"/>
+    <mergeCell ref="B59:B60"/>
+    <mergeCell ref="C59:C60"/>
+    <mergeCell ref="A61:A62"/>
+    <mergeCell ref="B61:B62"/>
+    <mergeCell ref="C61:C62"/>
+    <mergeCell ref="D61:D62"/>
+    <mergeCell ref="E61:E62"/>
+    <mergeCell ref="D59:D60"/>
+    <mergeCell ref="E59:E60"/>
+    <mergeCell ref="A57:A58"/>
+    <mergeCell ref="D74:D75"/>
+    <mergeCell ref="E74:E75"/>
+    <mergeCell ref="A70:A71"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="E72:E73"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="A77:A78"/>
+    <mergeCell ref="B77:B78"/>
+    <mergeCell ref="C77:C78"/>
+    <mergeCell ref="D77:D78"/>
+    <mergeCell ref="E77:E78"/>
+    <mergeCell ref="C81:C82"/>
+    <mergeCell ref="D81:D82"/>
+    <mergeCell ref="A81:A82"/>
+    <mergeCell ref="A83:A84"/>
+    <mergeCell ref="B83:B84"/>
+    <mergeCell ref="C83:C84"/>
+    <mergeCell ref="D83:D84"/>
+    <mergeCell ref="E83:E84"/>
+    <mergeCell ref="A79:A80"/>
+    <mergeCell ref="B79:B80"/>
+    <mergeCell ref="C79:C80"/>
+    <mergeCell ref="D79:D80"/>
+    <mergeCell ref="E79:E80"/>
+    <mergeCell ref="B81:B82"/>
+    <mergeCell ref="E81:E82"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="E33:E34"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="E35:E36"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="S5:T5"/>
+    <mergeCell ref="U5:V5"/>
+    <mergeCell ref="W5:X5"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="F4:F6"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G3:AL4"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="O6:P6"/>
+    <mergeCell ref="Q6:R6"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="U6:V6"/>
+    <mergeCell ref="W6:X6"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="D4:D6"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="O5:P5"/>
+    <mergeCell ref="Q5:R5"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
     <mergeCell ref="C22:C23"/>
     <mergeCell ref="C25:C26"/>
     <mergeCell ref="C29:C30"/>
@@ -41759,168 +41910,21 @@
     <mergeCell ref="D44:D45"/>
     <mergeCell ref="E44:E45"/>
     <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="E27:E28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="B3:B6"/>
-    <mergeCell ref="C4:C6"/>
-    <mergeCell ref="D4:D6"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="O5:P5"/>
-    <mergeCell ref="Q5:R5"/>
-    <mergeCell ref="E4:E6"/>
-    <mergeCell ref="S5:T5"/>
-    <mergeCell ref="U5:V5"/>
-    <mergeCell ref="W5:X5"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="F4:F6"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G3:AL4"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="O6:P6"/>
-    <mergeCell ref="Q6:R6"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="U6:V6"/>
-    <mergeCell ref="W6:X6"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="E33:E34"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="E35:E36"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="A77:A78"/>
-    <mergeCell ref="B77:B78"/>
-    <mergeCell ref="C77:C78"/>
-    <mergeCell ref="D77:D78"/>
-    <mergeCell ref="E77:E78"/>
-    <mergeCell ref="C81:C82"/>
-    <mergeCell ref="D81:D82"/>
-    <mergeCell ref="A81:A82"/>
-    <mergeCell ref="A83:A84"/>
-    <mergeCell ref="B83:B84"/>
-    <mergeCell ref="C83:C84"/>
-    <mergeCell ref="D83:D84"/>
-    <mergeCell ref="E83:E84"/>
-    <mergeCell ref="A79:A80"/>
-    <mergeCell ref="B79:B80"/>
-    <mergeCell ref="C79:C80"/>
-    <mergeCell ref="D79:D80"/>
-    <mergeCell ref="E79:E80"/>
-    <mergeCell ref="B81:B82"/>
-    <mergeCell ref="E81:E82"/>
-    <mergeCell ref="D74:D75"/>
-    <mergeCell ref="E74:E75"/>
-    <mergeCell ref="A70:A71"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="D72:D73"/>
-    <mergeCell ref="E72:E73"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="C74:C75"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="B51:B52"/>
-    <mergeCell ref="C51:C52"/>
-    <mergeCell ref="D51:D52"/>
-    <mergeCell ref="E51:E52"/>
-    <mergeCell ref="C70:C71"/>
-    <mergeCell ref="D70:D71"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="C68:C69"/>
-    <mergeCell ref="D68:D69"/>
-    <mergeCell ref="E68:E69"/>
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="E70:E71"/>
-    <mergeCell ref="B59:B60"/>
-    <mergeCell ref="C59:C60"/>
-    <mergeCell ref="A61:A62"/>
-    <mergeCell ref="B61:B62"/>
-    <mergeCell ref="C61:C62"/>
-    <mergeCell ref="D61:D62"/>
-    <mergeCell ref="E61:E62"/>
-    <mergeCell ref="D59:D60"/>
-    <mergeCell ref="E59:E60"/>
-    <mergeCell ref="A57:A58"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="E46:E47"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="D48:D49"/>
-    <mergeCell ref="E48:E49"/>
-    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="C57:C58"/>
+    <mergeCell ref="D57:D58"/>
+    <mergeCell ref="E57:E58"/>
+    <mergeCell ref="A59:A60"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="D66:D67"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="D64:D65"/>
+    <mergeCell ref="E64:E65"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="E66:E67"/>
   </mergeCells>
   <phoneticPr fontId="7"/>
   <dataValidations count="1">

--- a/進捗管理表/進捗管理表_森数.xlsx
+++ b/進捗管理表/進捗管理表_森数.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sensh\Documents\mytask\MyTaskSystem\進捗管理表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D15DB9BC-E3DE-4D47-B607-DFB375B99ACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{395EC4F7-737E-4DD1-B22B-B6DB5B178B50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="43">
   <si>
     <t>■進捗管理表</t>
   </si>
@@ -252,6 +252,13 @@
   </si>
   <si>
     <t>レビュー完了</t>
+  </si>
+  <si>
+    <t>DAO作成</t>
+    <rPh sb="3" eb="5">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
   </si>
 </sst>
 </file>
@@ -1046,44 +1053,29 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1121,8 +1113,23 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1433,142 +1440,142 @@
       <c r="AL2" s="2"/>
     </row>
     <row r="3" spans="1:38" ht="13.5" customHeight="1">
-      <c r="A3" s="52" t="s">
+      <c r="A3" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="54" t="s">
+      <c r="B3" s="70" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="64">
+      <c r="G3" s="59">
         <v>45705</v>
       </c>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="65"/>
-      <c r="K3" s="65"/>
-      <c r="L3" s="65"/>
-      <c r="M3" s="65"/>
-      <c r="N3" s="65"/>
-      <c r="O3" s="65"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="65"/>
-      <c r="U3" s="65"/>
-      <c r="V3" s="65"/>
-      <c r="W3" s="65"/>
-      <c r="X3" s="65"/>
-      <c r="Y3" s="65"/>
-      <c r="Z3" s="65"/>
-      <c r="AA3" s="65"/>
-      <c r="AB3" s="65"/>
-      <c r="AC3" s="65"/>
-      <c r="AD3" s="65"/>
-      <c r="AE3" s="65"/>
-      <c r="AF3" s="65"/>
-      <c r="AG3" s="65"/>
-      <c r="AH3" s="65"/>
-      <c r="AI3" s="65"/>
-      <c r="AJ3" s="65"/>
-      <c r="AK3" s="65"/>
-      <c r="AL3" s="66"/>
+      <c r="H3" s="60"/>
+      <c r="I3" s="60"/>
+      <c r="J3" s="60"/>
+      <c r="K3" s="60"/>
+      <c r="L3" s="60"/>
+      <c r="M3" s="60"/>
+      <c r="N3" s="60"/>
+      <c r="O3" s="60"/>
+      <c r="P3" s="60"/>
+      <c r="Q3" s="60"/>
+      <c r="R3" s="60"/>
+      <c r="S3" s="60"/>
+      <c r="T3" s="60"/>
+      <c r="U3" s="60"/>
+      <c r="V3" s="60"/>
+      <c r="W3" s="60"/>
+      <c r="X3" s="60"/>
+      <c r="Y3" s="60"/>
+      <c r="Z3" s="60"/>
+      <c r="AA3" s="60"/>
+      <c r="AB3" s="60"/>
+      <c r="AC3" s="60"/>
+      <c r="AD3" s="60"/>
+      <c r="AE3" s="60"/>
+      <c r="AF3" s="60"/>
+      <c r="AG3" s="60"/>
+      <c r="AH3" s="60"/>
+      <c r="AI3" s="60"/>
+      <c r="AJ3" s="60"/>
+      <c r="AK3" s="60"/>
+      <c r="AL3" s="61"/>
     </row>
     <row r="4" spans="1:38" ht="13.5" customHeight="1">
-      <c r="A4" s="53"/>
-      <c r="B4" s="53"/>
-      <c r="C4" s="55" t="s">
+      <c r="A4" s="69"/>
+      <c r="B4" s="69"/>
+      <c r="C4" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="52" t="s">
+      <c r="D4" s="68" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="58" t="s">
+      <c r="E4" s="73" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="61" t="s">
+      <c r="F4" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="67"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="68"/>
-      <c r="K4" s="68"/>
-      <c r="L4" s="68"/>
-      <c r="M4" s="68"/>
-      <c r="N4" s="68"/>
-      <c r="O4" s="68"/>
-      <c r="P4" s="68"/>
-      <c r="Q4" s="68"/>
-      <c r="R4" s="68"/>
-      <c r="S4" s="68"/>
-      <c r="T4" s="68"/>
-      <c r="U4" s="68"/>
-      <c r="V4" s="68"/>
-      <c r="W4" s="68"/>
-      <c r="X4" s="68"/>
-      <c r="Y4" s="68"/>
-      <c r="Z4" s="68"/>
-      <c r="AA4" s="68"/>
-      <c r="AB4" s="68"/>
-      <c r="AC4" s="68"/>
-      <c r="AD4" s="68"/>
-      <c r="AE4" s="68"/>
-      <c r="AF4" s="68"/>
-      <c r="AG4" s="68"/>
-      <c r="AH4" s="68"/>
-      <c r="AI4" s="68"/>
-      <c r="AJ4" s="68"/>
-      <c r="AK4" s="68"/>
-      <c r="AL4" s="69"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="63"/>
+      <c r="I4" s="63"/>
+      <c r="J4" s="63"/>
+      <c r="K4" s="63"/>
+      <c r="L4" s="63"/>
+      <c r="M4" s="63"/>
+      <c r="N4" s="63"/>
+      <c r="O4" s="63"/>
+      <c r="P4" s="63"/>
+      <c r="Q4" s="63"/>
+      <c r="R4" s="63"/>
+      <c r="S4" s="63"/>
+      <c r="T4" s="63"/>
+      <c r="U4" s="63"/>
+      <c r="V4" s="63"/>
+      <c r="W4" s="63"/>
+      <c r="X4" s="63"/>
+      <c r="Y4" s="63"/>
+      <c r="Z4" s="63"/>
+      <c r="AA4" s="63"/>
+      <c r="AB4" s="63"/>
+      <c r="AC4" s="63"/>
+      <c r="AD4" s="63"/>
+      <c r="AE4" s="63"/>
+      <c r="AF4" s="63"/>
+      <c r="AG4" s="63"/>
+      <c r="AH4" s="63"/>
+      <c r="AI4" s="63"/>
+      <c r="AJ4" s="63"/>
+      <c r="AK4" s="63"/>
+      <c r="AL4" s="64"/>
     </row>
     <row r="5" spans="1:38" ht="13.5" customHeight="1">
-      <c r="A5" s="53"/>
-      <c r="B5" s="53"/>
-      <c r="C5" s="53"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="53"/>
-      <c r="F5" s="62"/>
-      <c r="G5" s="59">
+      <c r="A5" s="69"/>
+      <c r="B5" s="69"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="53">
         <v>17</v>
       </c>
-      <c r="H5" s="60"/>
-      <c r="I5" s="56">
+      <c r="H5" s="54"/>
+      <c r="I5" s="55">
         <v>18</v>
       </c>
-      <c r="J5" s="57"/>
-      <c r="K5" s="56">
+      <c r="J5" s="72"/>
+      <c r="K5" s="55">
         <v>19</v>
       </c>
-      <c r="L5" s="57"/>
-      <c r="M5" s="56">
+      <c r="L5" s="72"/>
+      <c r="M5" s="55">
         <v>20</v>
       </c>
-      <c r="N5" s="57"/>
-      <c r="O5" s="56">
+      <c r="N5" s="72"/>
+      <c r="O5" s="55">
         <v>21</v>
       </c>
-      <c r="P5" s="57"/>
-      <c r="Q5" s="56">
+      <c r="P5" s="72"/>
+      <c r="Q5" s="55">
         <v>25</v>
       </c>
-      <c r="R5" s="57"/>
-      <c r="S5" s="59">
+      <c r="R5" s="72"/>
+      <c r="S5" s="53">
         <v>26</v>
       </c>
-      <c r="T5" s="60"/>
-      <c r="U5" s="56">
+      <c r="T5" s="54"/>
+      <c r="U5" s="55">
         <v>27</v>
       </c>
-      <c r="V5" s="60"/>
-      <c r="W5" s="56">
+      <c r="V5" s="54"/>
+      <c r="W5" s="55">
         <v>28</v>
       </c>
-      <c r="X5" s="60"/>
+      <c r="X5" s="54"/>
       <c r="Y5" s="10"/>
       <c r="Z5" s="10"/>
       <c r="AA5" s="10"/>
@@ -1585,48 +1592,48 @@
       <c r="AL5" s="11"/>
     </row>
     <row r="6" spans="1:38" ht="13.5" customHeight="1">
-      <c r="A6" s="49"/>
-      <c r="B6" s="49"/>
-      <c r="C6" s="49"/>
-      <c r="D6" s="49"/>
-      <c r="E6" s="49"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="59" t="s">
+      <c r="A6" s="50"/>
+      <c r="B6" s="50"/>
+      <c r="C6" s="50"/>
+      <c r="D6" s="50"/>
+      <c r="E6" s="50"/>
+      <c r="F6" s="58"/>
+      <c r="G6" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="60"/>
-      <c r="I6" s="70" t="s">
+      <c r="H6" s="54"/>
+      <c r="I6" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="J6" s="60"/>
-      <c r="K6" s="56" t="s">
+      <c r="J6" s="54"/>
+      <c r="K6" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="L6" s="60"/>
-      <c r="M6" s="56" t="s">
+      <c r="L6" s="54"/>
+      <c r="M6" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="N6" s="60"/>
-      <c r="O6" s="56" t="s">
+      <c r="N6" s="54"/>
+      <c r="O6" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="P6" s="60"/>
-      <c r="Q6" s="56" t="s">
+      <c r="P6" s="54"/>
+      <c r="Q6" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="R6" s="60"/>
-      <c r="S6" s="71" t="s">
+      <c r="R6" s="54"/>
+      <c r="S6" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="T6" s="60"/>
-      <c r="U6" s="72" t="s">
+      <c r="T6" s="54"/>
+      <c r="U6" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="V6" s="60"/>
-      <c r="W6" s="72" t="s">
+      <c r="V6" s="54"/>
+      <c r="W6" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="X6" s="60"/>
+      <c r="X6" s="54"/>
       <c r="Y6" s="12"/>
       <c r="Z6" s="12"/>
       <c r="AA6" s="12"/>
@@ -1685,12 +1692,12 @@
       <c r="AL7" s="20"/>
     </row>
     <row r="8" spans="1:38" ht="12" hidden="1" customHeight="1">
-      <c r="A8" s="51">
+      <c r="A8" s="49">
         <v>1</v>
       </c>
-      <c r="C8" s="48"/>
-      <c r="D8" s="48"/>
-      <c r="E8" s="48"/>
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="51"/>
       <c r="F8" s="21" t="s">
         <v>13</v>
       </c>
@@ -1728,10 +1735,10 @@
       <c r="AL8" s="26"/>
     </row>
     <row r="9" spans="1:38" ht="12" hidden="1" customHeight="1">
-      <c r="A9" s="49"/>
-      <c r="C9" s="49"/>
-      <c r="D9" s="49"/>
-      <c r="E9" s="49"/>
+      <c r="A9" s="50"/>
+      <c r="C9" s="50"/>
+      <c r="D9" s="50"/>
+      <c r="E9" s="50"/>
       <c r="F9" s="27" t="s">
         <v>14</v>
       </c>
@@ -1769,12 +1776,12 @@
       <c r="AL9" s="30"/>
     </row>
     <row r="10" spans="1:38" ht="12" hidden="1" customHeight="1">
-      <c r="A10" s="51">
+      <c r="A10" s="49">
         <v>2</v>
       </c>
-      <c r="C10" s="48"/>
-      <c r="D10" s="48"/>
-      <c r="E10" s="48"/>
+      <c r="C10" s="51"/>
+      <c r="D10" s="51"/>
+      <c r="E10" s="51"/>
       <c r="F10" s="31" t="s">
         <v>13</v>
       </c>
@@ -1812,10 +1819,10 @@
       <c r="AL10" s="10"/>
     </row>
     <row r="11" spans="1:38" ht="12" hidden="1" customHeight="1">
-      <c r="A11" s="49"/>
-      <c r="C11" s="49"/>
-      <c r="D11" s="49"/>
-      <c r="E11" s="49"/>
+      <c r="A11" s="50"/>
+      <c r="C11" s="50"/>
+      <c r="D11" s="50"/>
+      <c r="E11" s="50"/>
       <c r="F11" s="34" t="s">
         <v>14</v>
       </c>
@@ -1853,12 +1860,12 @@
       <c r="AL11" s="37"/>
     </row>
     <row r="12" spans="1:38" ht="12" hidden="1" customHeight="1">
-      <c r="A12" s="51">
+      <c r="A12" s="49">
         <v>3</v>
       </c>
-      <c r="C12" s="48"/>
-      <c r="D12" s="48"/>
-      <c r="E12" s="48"/>
+      <c r="C12" s="51"/>
+      <c r="D12" s="51"/>
+      <c r="E12" s="51"/>
       <c r="F12" s="21" t="s">
         <v>13</v>
       </c>
@@ -1896,10 +1903,10 @@
       <c r="AL12" s="26"/>
     </row>
     <row r="13" spans="1:38" ht="12" hidden="1" customHeight="1">
-      <c r="A13" s="49"/>
-      <c r="C13" s="49"/>
-      <c r="D13" s="49"/>
-      <c r="E13" s="49"/>
+      <c r="A13" s="50"/>
+      <c r="C13" s="50"/>
+      <c r="D13" s="50"/>
+      <c r="E13" s="50"/>
       <c r="F13" s="38" t="s">
         <v>14</v>
       </c>
@@ -1937,12 +1944,12 @@
       <c r="AL13" s="30"/>
     </row>
     <row r="14" spans="1:38" ht="12" hidden="1" customHeight="1">
-      <c r="A14" s="51">
+      <c r="A14" s="49">
         <v>4</v>
       </c>
-      <c r="C14" s="48"/>
-      <c r="D14" s="48"/>
-      <c r="E14" s="48"/>
+      <c r="C14" s="51"/>
+      <c r="D14" s="51"/>
+      <c r="E14" s="51"/>
       <c r="F14" s="31" t="s">
         <v>13</v>
       </c>
@@ -1980,10 +1987,10 @@
       <c r="AL14" s="10"/>
     </row>
     <row r="15" spans="1:38" ht="12" hidden="1" customHeight="1">
-      <c r="A15" s="49"/>
-      <c r="C15" s="49"/>
-      <c r="D15" s="49"/>
-      <c r="E15" s="49"/>
+      <c r="A15" s="50"/>
+      <c r="C15" s="50"/>
+      <c r="D15" s="50"/>
+      <c r="E15" s="50"/>
       <c r="F15" s="34" t="s">
         <v>14</v>
       </c>
@@ -2021,13 +2028,13 @@
       <c r="AL15" s="37"/>
     </row>
     <row r="16" spans="1:38" ht="12" hidden="1" customHeight="1">
-      <c r="A16" s="51">
+      <c r="A16" s="49">
         <v>5</v>
       </c>
-      <c r="B16" s="48"/>
-      <c r="C16" s="48"/>
-      <c r="D16" s="48"/>
-      <c r="E16" s="48"/>
+      <c r="B16" s="51"/>
+      <c r="C16" s="51"/>
+      <c r="D16" s="51"/>
+      <c r="E16" s="51"/>
       <c r="F16" s="21" t="s">
         <v>13</v>
       </c>
@@ -2065,11 +2072,11 @@
       <c r="AL16" s="26"/>
     </row>
     <row r="17" spans="1:38" ht="12" hidden="1" customHeight="1">
-      <c r="A17" s="49"/>
-      <c r="B17" s="49"/>
-      <c r="C17" s="49"/>
-      <c r="D17" s="49"/>
-      <c r="E17" s="49"/>
+      <c r="A17" s="50"/>
+      <c r="B17" s="50"/>
+      <c r="C17" s="50"/>
+      <c r="D17" s="50"/>
+      <c r="E17" s="50"/>
       <c r="F17" s="38" t="s">
         <v>14</v>
       </c>
@@ -2107,13 +2114,13 @@
       <c r="AL17" s="41"/>
     </row>
     <row r="18" spans="1:38" ht="12" hidden="1" customHeight="1">
-      <c r="A18" s="51">
+      <c r="A18" s="49">
         <v>6</v>
       </c>
-      <c r="B18" s="48"/>
-      <c r="C18" s="48"/>
-      <c r="D18" s="48"/>
-      <c r="E18" s="48"/>
+      <c r="B18" s="51"/>
+      <c r="C18" s="51"/>
+      <c r="D18" s="51"/>
+      <c r="E18" s="51"/>
       <c r="F18" s="31" t="s">
         <v>13</v>
       </c>
@@ -2151,11 +2158,11 @@
       <c r="AL18" s="10"/>
     </row>
     <row r="19" spans="1:38" ht="12" hidden="1" customHeight="1">
-      <c r="A19" s="49"/>
-      <c r="B19" s="49"/>
-      <c r="C19" s="49"/>
-      <c r="D19" s="49"/>
-      <c r="E19" s="49"/>
+      <c r="A19" s="50"/>
+      <c r="B19" s="50"/>
+      <c r="C19" s="50"/>
+      <c r="D19" s="50"/>
+      <c r="E19" s="50"/>
       <c r="F19" s="27" t="s">
         <v>14</v>
       </c>
@@ -2193,13 +2200,13 @@
       <c r="AL19" s="41"/>
     </row>
     <row r="20" spans="1:38" ht="12" hidden="1" customHeight="1">
-      <c r="A20" s="51">
+      <c r="A20" s="49">
         <v>7</v>
       </c>
-      <c r="B20" s="48"/>
-      <c r="C20" s="48"/>
-      <c r="D20" s="48"/>
-      <c r="E20" s="48"/>
+      <c r="B20" s="51"/>
+      <c r="C20" s="51"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="51"/>
       <c r="F20" s="31" t="s">
         <v>13</v>
       </c>
@@ -2237,11 +2244,11 @@
       <c r="AL20" s="10"/>
     </row>
     <row r="21" spans="1:38" ht="12" hidden="1" customHeight="1">
-      <c r="A21" s="49"/>
-      <c r="B21" s="49"/>
-      <c r="C21" s="49"/>
-      <c r="D21" s="49"/>
-      <c r="E21" s="49"/>
+      <c r="A21" s="50"/>
+      <c r="B21" s="50"/>
+      <c r="C21" s="50"/>
+      <c r="D21" s="50"/>
+      <c r="E21" s="50"/>
       <c r="F21" s="27" t="s">
         <v>14</v>
       </c>
@@ -2279,13 +2286,13 @@
       <c r="AL21" s="41"/>
     </row>
     <row r="22" spans="1:38" ht="12" hidden="1" customHeight="1">
-      <c r="A22" s="51">
+      <c r="A22" s="49">
         <v>8</v>
       </c>
-      <c r="B22" s="48"/>
-      <c r="C22" s="48"/>
-      <c r="D22" s="48"/>
-      <c r="E22" s="48"/>
+      <c r="B22" s="51"/>
+      <c r="C22" s="51"/>
+      <c r="D22" s="51"/>
+      <c r="E22" s="51"/>
       <c r="F22" s="21" t="s">
         <v>13</v>
       </c>
@@ -2323,11 +2330,11 @@
       <c r="AL22" s="26"/>
     </row>
     <row r="23" spans="1:38" ht="12" hidden="1" customHeight="1">
-      <c r="A23" s="49"/>
-      <c r="B23" s="49"/>
-      <c r="C23" s="49"/>
-      <c r="D23" s="49"/>
-      <c r="E23" s="49"/>
+      <c r="A23" s="50"/>
+      <c r="B23" s="50"/>
+      <c r="C23" s="50"/>
+      <c r="D23" s="50"/>
+      <c r="E23" s="50"/>
       <c r="F23" s="34" t="s">
         <v>14</v>
       </c>
@@ -2407,19 +2414,19 @@
       <c r="AL24" s="20"/>
     </row>
     <row r="25" spans="1:38" ht="12" customHeight="1">
-      <c r="A25" s="51">
+      <c r="A25" s="49">
         <v>1</v>
       </c>
-      <c r="B25" s="48" t="s">
+      <c r="B25" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="48">
+      <c r="C25" s="51">
         <v>0.5</v>
       </c>
-      <c r="D25" s="48" t="s">
+      <c r="D25" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="E25" s="48" t="s">
+      <c r="E25" s="51" t="s">
         <v>40</v>
       </c>
       <c r="F25" s="21" t="s">
@@ -2459,11 +2466,11 @@
       <c r="AL25" s="26"/>
     </row>
     <row r="26" spans="1:38" ht="12" customHeight="1">
-      <c r="A26" s="49"/>
-      <c r="B26" s="49"/>
-      <c r="C26" s="49"/>
-      <c r="D26" s="49"/>
-      <c r="E26" s="50"/>
+      <c r="A26" s="50"/>
+      <c r="B26" s="50"/>
+      <c r="C26" s="50"/>
+      <c r="D26" s="50"/>
+      <c r="E26" s="52"/>
       <c r="F26" s="27" t="s">
         <v>14</v>
       </c>
@@ -2501,19 +2508,19 @@
       <c r="AL26" s="30"/>
     </row>
     <row r="27" spans="1:38" ht="12" customHeight="1">
-      <c r="A27" s="51">
+      <c r="A27" s="49">
         <v>2</v>
       </c>
-      <c r="B27" s="48" t="s">
+      <c r="B27" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="48">
+      <c r="C27" s="51">
         <v>1</v>
       </c>
-      <c r="D27" s="48" t="s">
+      <c r="D27" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="E27" s="48" t="s">
+      <c r="E27" s="51" t="s">
         <v>40</v>
       </c>
       <c r="F27" s="31" t="s">
@@ -2553,11 +2560,11 @@
       <c r="AL27" s="10"/>
     </row>
     <row r="28" spans="1:38" ht="12" customHeight="1">
-      <c r="A28" s="49"/>
-      <c r="B28" s="49"/>
-      <c r="C28" s="49"/>
-      <c r="D28" s="49"/>
-      <c r="E28" s="50"/>
+      <c r="A28" s="50"/>
+      <c r="B28" s="50"/>
+      <c r="C28" s="50"/>
+      <c r="D28" s="50"/>
+      <c r="E28" s="52"/>
       <c r="F28" s="34" t="s">
         <v>14</v>
       </c>
@@ -2595,19 +2602,19 @@
       <c r="AL28" s="37"/>
     </row>
     <row r="29" spans="1:38" ht="12" customHeight="1">
-      <c r="A29" s="51">
+      <c r="A29" s="49">
         <v>3</v>
       </c>
-      <c r="B29" s="48" t="s">
+      <c r="B29" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="48">
+      <c r="C29" s="51">
         <v>1</v>
       </c>
-      <c r="D29" s="48" t="s">
+      <c r="D29" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="E29" s="48" t="s">
+      <c r="E29" s="51" t="s">
         <v>40</v>
       </c>
       <c r="F29" s="21" t="s">
@@ -2647,18 +2654,18 @@
       <c r="AL29" s="26"/>
     </row>
     <row r="30" spans="1:38" ht="12" customHeight="1">
-      <c r="A30" s="49"/>
-      <c r="B30" s="49"/>
-      <c r="C30" s="49"/>
-      <c r="D30" s="49"/>
-      <c r="E30" s="50"/>
+      <c r="A30" s="50"/>
+      <c r="B30" s="50"/>
+      <c r="C30" s="50"/>
+      <c r="D30" s="50"/>
+      <c r="E30" s="52"/>
       <c r="F30" s="38" t="s">
         <v>14</v>
       </c>
       <c r="G30" s="39"/>
       <c r="H30" s="40"/>
       <c r="I30" s="40"/>
-      <c r="J30" s="73"/>
+      <c r="J30" s="48"/>
       <c r="K30" s="40"/>
       <c r="L30" s="40"/>
       <c r="M30" s="40"/>
@@ -2689,19 +2696,19 @@
       <c r="AL30" s="30"/>
     </row>
     <row r="31" spans="1:38" ht="12" customHeight="1">
-      <c r="A31" s="51">
+      <c r="A31" s="49">
         <v>4</v>
       </c>
-      <c r="B31" s="48" t="s">
+      <c r="B31" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="C31" s="48">
+      <c r="C31" s="51">
         <v>1</v>
       </c>
-      <c r="D31" s="48" t="s">
+      <c r="D31" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="E31" s="48" t="s">
+      <c r="E31" s="51" t="s">
         <v>41</v>
       </c>
       <c r="F31" s="31" t="s">
@@ -2741,11 +2748,11 @@
       <c r="AL31" s="10"/>
     </row>
     <row r="32" spans="1:38" ht="12" customHeight="1">
-      <c r="A32" s="49"/>
-      <c r="B32" s="49"/>
-      <c r="C32" s="49"/>
-      <c r="D32" s="49"/>
-      <c r="E32" s="50"/>
+      <c r="A32" s="50"/>
+      <c r="B32" s="50"/>
+      <c r="C32" s="50"/>
+      <c r="D32" s="50"/>
+      <c r="E32" s="52"/>
       <c r="F32" s="34" t="s">
         <v>14</v>
       </c>
@@ -2783,13 +2790,13 @@
       <c r="AL32" s="37"/>
     </row>
     <row r="33" spans="1:38" ht="12" customHeight="1">
-      <c r="A33" s="51">
+      <c r="A33" s="49">
         <v>5</v>
       </c>
-      <c r="B33" s="48"/>
-      <c r="C33" s="48"/>
-      <c r="D33" s="48"/>
-      <c r="E33" s="48"/>
+      <c r="B33" s="51"/>
+      <c r="C33" s="51"/>
+      <c r="D33" s="51"/>
+      <c r="E33" s="51"/>
       <c r="F33" s="21" t="s">
         <v>13</v>
       </c>
@@ -2826,11 +2833,11 @@
       <c r="AL33" s="26"/>
     </row>
     <row r="34" spans="1:38" ht="12" customHeight="1">
-      <c r="A34" s="49"/>
-      <c r="B34" s="49"/>
-      <c r="C34" s="49"/>
-      <c r="D34" s="49"/>
-      <c r="E34" s="50"/>
+      <c r="A34" s="50"/>
+      <c r="B34" s="50"/>
+      <c r="C34" s="50"/>
+      <c r="D34" s="50"/>
+      <c r="E34" s="52"/>
       <c r="F34" s="38" t="s">
         <v>14</v>
       </c>
@@ -2868,13 +2875,13 @@
       <c r="AL34" s="41"/>
     </row>
     <row r="35" spans="1:38" ht="12" customHeight="1">
-      <c r="A35" s="51">
+      <c r="A35" s="49">
         <v>6</v>
       </c>
-      <c r="B35" s="48"/>
-      <c r="C35" s="48"/>
-      <c r="D35" s="48"/>
-      <c r="E35" s="48"/>
+      <c r="B35" s="51"/>
+      <c r="C35" s="51"/>
+      <c r="D35" s="51"/>
+      <c r="E35" s="51"/>
       <c r="F35" s="31" t="s">
         <v>13</v>
       </c>
@@ -2912,11 +2919,11 @@
       <c r="AL35" s="10"/>
     </row>
     <row r="36" spans="1:38" ht="12" customHeight="1">
-      <c r="A36" s="49"/>
-      <c r="B36" s="49"/>
-      <c r="C36" s="49"/>
-      <c r="D36" s="49"/>
-      <c r="E36" s="49"/>
+      <c r="A36" s="50"/>
+      <c r="B36" s="50"/>
+      <c r="C36" s="50"/>
+      <c r="D36" s="50"/>
+      <c r="E36" s="50"/>
       <c r="F36" s="34" t="s">
         <v>14</v>
       </c>
@@ -2996,20 +3003,20 @@
       <c r="AL37" s="20"/>
     </row>
     <row r="38" spans="1:38" ht="12" customHeight="1">
-      <c r="A38" s="51">
+      <c r="A38" s="49">
         <v>1</v>
       </c>
-      <c r="B38" s="48" t="s">
+      <c r="B38" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="C38" s="48">
+      <c r="C38" s="51">
         <v>3</v>
       </c>
-      <c r="D38" s="48" t="s">
+      <c r="D38" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="E38" s="48" t="s">
-        <v>39</v>
+      <c r="E38" s="51" t="s">
+        <v>40</v>
       </c>
       <c r="F38" s="21" t="s">
         <v>13</v>
@@ -3048,11 +3055,11 @@
       <c r="AL38" s="26"/>
     </row>
     <row r="39" spans="1:38" ht="12" customHeight="1">
-      <c r="A39" s="49"/>
-      <c r="B39" s="49"/>
-      <c r="C39" s="49"/>
-      <c r="D39" s="49"/>
-      <c r="E39" s="50"/>
+      <c r="A39" s="50"/>
+      <c r="B39" s="50"/>
+      <c r="C39" s="50"/>
+      <c r="D39" s="50"/>
+      <c r="E39" s="52"/>
       <c r="F39" s="27" t="s">
         <v>14</v>
       </c>
@@ -3062,7 +3069,7 @@
       <c r="J39" s="29"/>
       <c r="K39" s="29"/>
       <c r="L39" s="29"/>
-      <c r="M39" s="29"/>
+      <c r="M39" s="46"/>
       <c r="N39" s="29"/>
       <c r="O39" s="29"/>
       <c r="P39" s="29"/>
@@ -3090,20 +3097,20 @@
       <c r="AL39" s="30"/>
     </row>
     <row r="40" spans="1:38" ht="12" customHeight="1">
-      <c r="A40" s="51">
+      <c r="A40" s="49">
         <v>2</v>
       </c>
-      <c r="B40" s="48" t="s">
+      <c r="B40" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="C40" s="48">
+      <c r="C40" s="51">
         <v>1</v>
       </c>
-      <c r="D40" s="48" t="s">
+      <c r="D40" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="E40" s="48" t="s">
-        <v>39</v>
+      <c r="E40" s="51" t="s">
+        <v>40</v>
       </c>
       <c r="F40" s="31" t="s">
         <v>13</v>
@@ -3142,11 +3149,11 @@
       <c r="AL40" s="10"/>
     </row>
     <row r="41" spans="1:38" ht="12" customHeight="1">
-      <c r="A41" s="49"/>
-      <c r="B41" s="49"/>
-      <c r="C41" s="49"/>
-      <c r="D41" s="49"/>
-      <c r="E41" s="50"/>
+      <c r="A41" s="50"/>
+      <c r="B41" s="50"/>
+      <c r="C41" s="50"/>
+      <c r="D41" s="50"/>
+      <c r="E41" s="52"/>
       <c r="F41" s="34" t="s">
         <v>14</v>
       </c>
@@ -3157,7 +3164,7 @@
       <c r="K41" s="36"/>
       <c r="L41" s="36"/>
       <c r="M41" s="36"/>
-      <c r="N41" s="36"/>
+      <c r="N41" s="47"/>
       <c r="O41" s="36"/>
       <c r="P41" s="36"/>
       <c r="Q41" s="36"/>
@@ -3184,20 +3191,20 @@
       <c r="AL41" s="37"/>
     </row>
     <row r="42" spans="1:38" ht="12" customHeight="1">
-      <c r="A42" s="51">
+      <c r="A42" s="49">
         <v>3</v>
       </c>
-      <c r="B42" s="48" t="s">
+      <c r="B42" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="C42" s="48">
+      <c r="C42" s="51">
         <v>4</v>
       </c>
-      <c r="D42" s="48" t="s">
+      <c r="D42" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="E42" s="48" t="s">
-        <v>35</v>
+      <c r="E42" s="51" t="s">
+        <v>39</v>
       </c>
       <c r="F42" s="21" t="s">
         <v>13</v>
@@ -3236,11 +3243,11 @@
       <c r="AL42" s="26"/>
     </row>
     <row r="43" spans="1:38" ht="12" customHeight="1">
-      <c r="A43" s="49"/>
-      <c r="B43" s="50"/>
-      <c r="C43" s="49"/>
-      <c r="D43" s="49"/>
-      <c r="E43" s="50"/>
+      <c r="A43" s="50"/>
+      <c r="B43" s="52"/>
+      <c r="C43" s="50"/>
+      <c r="D43" s="50"/>
+      <c r="E43" s="52"/>
       <c r="F43" s="38" t="s">
         <v>14</v>
       </c>
@@ -3278,20 +3285,20 @@
       <c r="AL43" s="30"/>
     </row>
     <row r="44" spans="1:38" ht="12" customHeight="1">
-      <c r="A44" s="51">
+      <c r="A44" s="49">
         <v>4</v>
       </c>
-      <c r="B44" s="48" t="s">
-        <v>36</v>
+      <c r="B44" s="51" t="s">
+        <v>42</v>
       </c>
-      <c r="C44" s="48">
+      <c r="C44" s="51">
         <v>2</v>
       </c>
-      <c r="D44" s="48" t="s">
+      <c r="D44" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="E44" s="48" t="s">
-        <v>35</v>
+      <c r="E44" s="51" t="s">
+        <v>39</v>
       </c>
       <c r="F44" s="31" t="s">
         <v>13</v>
@@ -3329,11 +3336,11 @@
       <c r="AL44" s="10"/>
     </row>
     <row r="45" spans="1:38" ht="12" customHeight="1">
-      <c r="A45" s="49"/>
-      <c r="B45" s="49"/>
-      <c r="C45" s="49"/>
-      <c r="D45" s="49"/>
-      <c r="E45" s="50"/>
+      <c r="A45" s="50"/>
+      <c r="B45" s="52"/>
+      <c r="C45" s="50"/>
+      <c r="D45" s="50"/>
+      <c r="E45" s="52"/>
       <c r="F45" s="34" t="s">
         <v>14</v>
       </c>
@@ -3371,13 +3378,19 @@
       <c r="AL45" s="37"/>
     </row>
     <row r="46" spans="1:38" ht="12" customHeight="1">
-      <c r="A46" s="51">
+      <c r="A46" s="49">
         <v>5</v>
       </c>
-      <c r="B46" s="48"/>
-      <c r="C46" s="48"/>
-      <c r="D46" s="48"/>
-      <c r="E46" s="48"/>
+      <c r="B46" s="51" t="s">
+        <v>36</v>
+      </c>
+      <c r="C46" s="51">
+        <v>1</v>
+      </c>
+      <c r="D46" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="E46" s="51"/>
       <c r="F46" s="21" t="s">
         <v>13</v>
       </c>
@@ -3415,11 +3428,11 @@
       <c r="AL46" s="26"/>
     </row>
     <row r="47" spans="1:38" ht="12" customHeight="1">
-      <c r="A47" s="49"/>
-      <c r="B47" s="49"/>
-      <c r="C47" s="49"/>
-      <c r="D47" s="49"/>
-      <c r="E47" s="49"/>
+      <c r="A47" s="50"/>
+      <c r="B47" s="50"/>
+      <c r="C47" s="50"/>
+      <c r="D47" s="50"/>
+      <c r="E47" s="50"/>
       <c r="F47" s="38" t="s">
         <v>14</v>
       </c>
@@ -3457,13 +3470,13 @@
       <c r="AL47" s="41"/>
     </row>
     <row r="48" spans="1:38" ht="12" customHeight="1">
-      <c r="A48" s="51">
+      <c r="A48" s="49">
         <v>6</v>
       </c>
-      <c r="B48" s="48"/>
-      <c r="C48" s="48"/>
-      <c r="D48" s="48"/>
-      <c r="E48" s="48"/>
+      <c r="B48" s="51"/>
+      <c r="C48" s="51"/>
+      <c r="D48" s="51"/>
+      <c r="E48" s="51"/>
       <c r="F48" s="31" t="s">
         <v>13</v>
       </c>
@@ -3501,11 +3514,11 @@
       <c r="AL48" s="10"/>
     </row>
     <row r="49" spans="1:38" ht="12" customHeight="1">
-      <c r="A49" s="49"/>
-      <c r="B49" s="49"/>
-      <c r="C49" s="49"/>
-      <c r="D49" s="49"/>
-      <c r="E49" s="49"/>
+      <c r="A49" s="50"/>
+      <c r="B49" s="50"/>
+      <c r="C49" s="50"/>
+      <c r="D49" s="50"/>
+      <c r="E49" s="50"/>
       <c r="F49" s="34" t="s">
         <v>14</v>
       </c>
@@ -3585,19 +3598,19 @@
       <c r="AL50" s="20"/>
     </row>
     <row r="51" spans="1:38" ht="12" customHeight="1">
-      <c r="A51" s="51">
+      <c r="A51" s="49">
         <v>1</v>
       </c>
-      <c r="B51" s="48" t="s">
+      <c r="B51" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="C51" s="48">
+      <c r="C51" s="51">
         <v>4</v>
       </c>
-      <c r="D51" s="48" t="s">
+      <c r="D51" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="E51" s="48" t="s">
+      <c r="E51" s="51" t="s">
         <v>35</v>
       </c>
       <c r="F51" s="21" t="s">
@@ -3637,11 +3650,11 @@
       <c r="AL51" s="26"/>
     </row>
     <row r="52" spans="1:38" ht="12" customHeight="1">
-      <c r="A52" s="49"/>
-      <c r="B52" s="49"/>
-      <c r="C52" s="49"/>
-      <c r="D52" s="49"/>
-      <c r="E52" s="50"/>
+      <c r="A52" s="50"/>
+      <c r="B52" s="50"/>
+      <c r="C52" s="50"/>
+      <c r="D52" s="50"/>
+      <c r="E52" s="52"/>
       <c r="F52" s="27" t="s">
         <v>14</v>
       </c>
@@ -3679,19 +3692,19 @@
       <c r="AL52" s="30"/>
     </row>
     <row r="53" spans="1:38" ht="12" customHeight="1">
-      <c r="A53" s="51">
+      <c r="A53" s="49">
         <v>2</v>
       </c>
-      <c r="B53" s="48" t="s">
+      <c r="B53" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="C53" s="48">
+      <c r="C53" s="51">
         <v>4</v>
       </c>
-      <c r="D53" s="48" t="s">
+      <c r="D53" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="E53" s="48" t="s">
+      <c r="E53" s="51" t="s">
         <v>35</v>
       </c>
       <c r="F53" s="31" t="s">
@@ -3731,11 +3744,11 @@
       <c r="AL53" s="10"/>
     </row>
     <row r="54" spans="1:38" ht="12" customHeight="1">
-      <c r="A54" s="49"/>
-      <c r="B54" s="49"/>
-      <c r="C54" s="49"/>
-      <c r="D54" s="50"/>
-      <c r="E54" s="50"/>
+      <c r="A54" s="50"/>
+      <c r="B54" s="50"/>
+      <c r="C54" s="50"/>
+      <c r="D54" s="52"/>
+      <c r="E54" s="52"/>
       <c r="F54" s="34" t="s">
         <v>14</v>
       </c>
@@ -3773,19 +3786,19 @@
       <c r="AL54" s="37"/>
     </row>
     <row r="55" spans="1:38" ht="12" customHeight="1">
-      <c r="A55" s="51">
+      <c r="A55" s="49">
         <v>3</v>
       </c>
-      <c r="B55" s="48" t="s">
+      <c r="B55" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="C55" s="48">
+      <c r="C55" s="51">
         <v>2</v>
       </c>
-      <c r="D55" s="48" t="s">
+      <c r="D55" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="E55" s="48" t="s">
+      <c r="E55" s="51" t="s">
         <v>35</v>
       </c>
       <c r="F55" s="21" t="s">
@@ -3825,11 +3838,11 @@
       <c r="AL55" s="26"/>
     </row>
     <row r="56" spans="1:38" ht="12" customHeight="1">
-      <c r="A56" s="49"/>
-      <c r="B56" s="49"/>
-      <c r="C56" s="49"/>
-      <c r="D56" s="50"/>
-      <c r="E56" s="50"/>
+      <c r="A56" s="50"/>
+      <c r="B56" s="50"/>
+      <c r="C56" s="50"/>
+      <c r="D56" s="52"/>
+      <c r="E56" s="52"/>
       <c r="F56" s="38" t="s">
         <v>14</v>
       </c>
@@ -3867,19 +3880,19 @@
       <c r="AL56" s="30"/>
     </row>
     <row r="57" spans="1:38" ht="12" customHeight="1">
-      <c r="A57" s="51">
+      <c r="A57" s="49">
         <v>4</v>
       </c>
-      <c r="B57" s="48" t="s">
+      <c r="B57" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="C57" s="48">
+      <c r="C57" s="51">
         <v>3</v>
       </c>
-      <c r="D57" s="48" t="s">
+      <c r="D57" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="E57" s="48" t="s">
+      <c r="E57" s="51" t="s">
         <v>35</v>
       </c>
       <c r="F57" s="31" t="s">
@@ -3919,11 +3932,11 @@
       <c r="AL57" s="10"/>
     </row>
     <row r="58" spans="1:38" ht="12" customHeight="1">
-      <c r="A58" s="49"/>
-      <c r="B58" s="49"/>
-      <c r="C58" s="49"/>
-      <c r="D58" s="50"/>
-      <c r="E58" s="50"/>
+      <c r="A58" s="50"/>
+      <c r="B58" s="50"/>
+      <c r="C58" s="50"/>
+      <c r="D58" s="52"/>
+      <c r="E58" s="52"/>
       <c r="F58" s="34" t="s">
         <v>14</v>
       </c>
@@ -3961,13 +3974,13 @@
       <c r="AL58" s="37"/>
     </row>
     <row r="59" spans="1:38" ht="12" customHeight="1">
-      <c r="A59" s="51">
+      <c r="A59" s="49">
         <v>5</v>
       </c>
-      <c r="B59" s="48"/>
-      <c r="C59" s="48"/>
-      <c r="D59" s="48"/>
-      <c r="E59" s="48"/>
+      <c r="B59" s="51"/>
+      <c r="C59" s="51"/>
+      <c r="D59" s="51"/>
+      <c r="E59" s="51"/>
       <c r="F59" s="21" t="s">
         <v>13</v>
       </c>
@@ -4005,11 +4018,11 @@
       <c r="AL59" s="26"/>
     </row>
     <row r="60" spans="1:38" ht="12" customHeight="1">
-      <c r="A60" s="49"/>
-      <c r="B60" s="49"/>
-      <c r="C60" s="49"/>
-      <c r="D60" s="49"/>
-      <c r="E60" s="49"/>
+      <c r="A60" s="50"/>
+      <c r="B60" s="50"/>
+      <c r="C60" s="50"/>
+      <c r="D60" s="50"/>
+      <c r="E60" s="50"/>
       <c r="F60" s="38" t="s">
         <v>14</v>
       </c>
@@ -4047,13 +4060,13 @@
       <c r="AL60" s="41"/>
     </row>
     <row r="61" spans="1:38" ht="12" customHeight="1">
-      <c r="A61" s="51">
+      <c r="A61" s="49">
         <v>6</v>
       </c>
-      <c r="B61" s="48"/>
-      <c r="C61" s="48"/>
-      <c r="D61" s="48"/>
-      <c r="E61" s="48"/>
+      <c r="B61" s="51"/>
+      <c r="C61" s="51"/>
+      <c r="D61" s="51"/>
+      <c r="E61" s="51"/>
       <c r="F61" s="31" t="s">
         <v>13</v>
       </c>
@@ -4091,11 +4104,11 @@
       <c r="AL61" s="10"/>
     </row>
     <row r="62" spans="1:38" ht="12" customHeight="1">
-      <c r="A62" s="49"/>
-      <c r="B62" s="49"/>
-      <c r="C62" s="49"/>
-      <c r="D62" s="49"/>
-      <c r="E62" s="49"/>
+      <c r="A62" s="50"/>
+      <c r="B62" s="50"/>
+      <c r="C62" s="50"/>
+      <c r="D62" s="50"/>
+      <c r="E62" s="50"/>
       <c r="F62" s="34" t="s">
         <v>14</v>
       </c>
@@ -4175,19 +4188,19 @@
       <c r="AL63" s="20"/>
     </row>
     <row r="64" spans="1:38" ht="12" customHeight="1">
-      <c r="A64" s="51">
+      <c r="A64" s="49">
         <v>1</v>
       </c>
-      <c r="B64" s="48" t="s">
+      <c r="B64" s="51" t="s">
         <v>37</v>
       </c>
-      <c r="C64" s="48">
+      <c r="C64" s="51">
         <v>2</v>
       </c>
-      <c r="D64" s="48" t="s">
+      <c r="D64" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="E64" s="48" t="s">
+      <c r="E64" s="51" t="s">
         <v>38</v>
       </c>
       <c r="F64" s="21" t="s">
@@ -4227,11 +4240,11 @@
       <c r="AL64" s="26"/>
     </row>
     <row r="65" spans="1:38" ht="12" customHeight="1">
-      <c r="A65" s="49"/>
-      <c r="B65" s="49"/>
-      <c r="C65" s="49"/>
-      <c r="D65" s="49"/>
-      <c r="E65" s="49"/>
+      <c r="A65" s="50"/>
+      <c r="B65" s="50"/>
+      <c r="C65" s="50"/>
+      <c r="D65" s="50"/>
+      <c r="E65" s="50"/>
       <c r="F65" s="27" t="s">
         <v>14</v>
       </c>
@@ -4269,13 +4282,13 @@
       <c r="AL65" s="30"/>
     </row>
     <row r="66" spans="1:38" ht="12" customHeight="1">
-      <c r="A66" s="51">
+      <c r="A66" s="49">
         <v>2</v>
       </c>
-      <c r="B66" s="48"/>
-      <c r="C66" s="48"/>
-      <c r="D66" s="48"/>
-      <c r="E66" s="48"/>
+      <c r="B66" s="51"/>
+      <c r="C66" s="51"/>
+      <c r="D66" s="51"/>
+      <c r="E66" s="51"/>
       <c r="F66" s="31" t="s">
         <v>13</v>
       </c>
@@ -4313,11 +4326,11 @@
       <c r="AL66" s="10"/>
     </row>
     <row r="67" spans="1:38" ht="12" customHeight="1">
-      <c r="A67" s="49"/>
-      <c r="B67" s="49"/>
-      <c r="C67" s="49"/>
-      <c r="D67" s="49"/>
-      <c r="E67" s="49"/>
+      <c r="A67" s="50"/>
+      <c r="B67" s="50"/>
+      <c r="C67" s="50"/>
+      <c r="D67" s="50"/>
+      <c r="E67" s="50"/>
       <c r="F67" s="34" t="s">
         <v>14</v>
       </c>
@@ -4355,13 +4368,13 @@
       <c r="AL67" s="37"/>
     </row>
     <row r="68" spans="1:38" ht="12" customHeight="1">
-      <c r="A68" s="51">
+      <c r="A68" s="49">
         <v>3</v>
       </c>
-      <c r="B68" s="48"/>
-      <c r="C68" s="48"/>
-      <c r="D68" s="48"/>
-      <c r="E68" s="48"/>
+      <c r="B68" s="51"/>
+      <c r="C68" s="51"/>
+      <c r="D68" s="51"/>
+      <c r="E68" s="51"/>
       <c r="F68" s="21" t="s">
         <v>13</v>
       </c>
@@ -4399,11 +4412,11 @@
       <c r="AL68" s="26"/>
     </row>
     <row r="69" spans="1:38" ht="12" customHeight="1">
-      <c r="A69" s="49"/>
-      <c r="B69" s="49"/>
-      <c r="C69" s="49"/>
-      <c r="D69" s="49"/>
-      <c r="E69" s="49"/>
+      <c r="A69" s="50"/>
+      <c r="B69" s="50"/>
+      <c r="C69" s="50"/>
+      <c r="D69" s="50"/>
+      <c r="E69" s="50"/>
       <c r="F69" s="38" t="s">
         <v>14</v>
       </c>
@@ -4441,13 +4454,13 @@
       <c r="AL69" s="30"/>
     </row>
     <row r="70" spans="1:38" ht="12" customHeight="1">
-      <c r="A70" s="51">
+      <c r="A70" s="49">
         <v>4</v>
       </c>
-      <c r="B70" s="48"/>
-      <c r="C70" s="48"/>
-      <c r="D70" s="48"/>
-      <c r="E70" s="48"/>
+      <c r="B70" s="51"/>
+      <c r="C70" s="51"/>
+      <c r="D70" s="51"/>
+      <c r="E70" s="51"/>
       <c r="F70" s="31" t="s">
         <v>13</v>
       </c>
@@ -4485,11 +4498,11 @@
       <c r="AL70" s="10"/>
     </row>
     <row r="71" spans="1:38" ht="12" customHeight="1">
-      <c r="A71" s="49"/>
-      <c r="B71" s="49"/>
-      <c r="C71" s="49"/>
-      <c r="D71" s="49"/>
-      <c r="E71" s="49"/>
+      <c r="A71" s="50"/>
+      <c r="B71" s="50"/>
+      <c r="C71" s="50"/>
+      <c r="D71" s="50"/>
+      <c r="E71" s="50"/>
       <c r="F71" s="34" t="s">
         <v>14</v>
       </c>
@@ -4527,13 +4540,13 @@
       <c r="AL71" s="37"/>
     </row>
     <row r="72" spans="1:38" ht="12" customHeight="1">
-      <c r="A72" s="51">
+      <c r="A72" s="49">
         <v>5</v>
       </c>
-      <c r="B72" s="48"/>
-      <c r="C72" s="48"/>
-      <c r="D72" s="48"/>
-      <c r="E72" s="48"/>
+      <c r="B72" s="51"/>
+      <c r="C72" s="51"/>
+      <c r="D72" s="51"/>
+      <c r="E72" s="51"/>
       <c r="F72" s="21" t="s">
         <v>13</v>
       </c>
@@ -4571,11 +4584,11 @@
       <c r="AL72" s="26"/>
     </row>
     <row r="73" spans="1:38" ht="12" customHeight="1">
-      <c r="A73" s="49"/>
-      <c r="B73" s="49"/>
-      <c r="C73" s="49"/>
-      <c r="D73" s="49"/>
-      <c r="E73" s="49"/>
+      <c r="A73" s="50"/>
+      <c r="B73" s="50"/>
+      <c r="C73" s="50"/>
+      <c r="D73" s="50"/>
+      <c r="E73" s="50"/>
       <c r="F73" s="38" t="s">
         <v>14</v>
       </c>
@@ -4613,13 +4626,13 @@
       <c r="AL73" s="41"/>
     </row>
     <row r="74" spans="1:38" ht="12" customHeight="1">
-      <c r="A74" s="51">
+      <c r="A74" s="49">
         <v>6</v>
       </c>
-      <c r="B74" s="48"/>
-      <c r="C74" s="48"/>
-      <c r="D74" s="48"/>
-      <c r="E74" s="48"/>
+      <c r="B74" s="51"/>
+      <c r="C74" s="51"/>
+      <c r="D74" s="51"/>
+      <c r="E74" s="51"/>
       <c r="F74" s="31" t="s">
         <v>13</v>
       </c>
@@ -4657,11 +4670,11 @@
       <c r="AL74" s="10"/>
     </row>
     <row r="75" spans="1:38" ht="12" customHeight="1">
-      <c r="A75" s="49"/>
-      <c r="B75" s="49"/>
-      <c r="C75" s="49"/>
-      <c r="D75" s="49"/>
-      <c r="E75" s="49"/>
+      <c r="A75" s="50"/>
+      <c r="B75" s="50"/>
+      <c r="C75" s="50"/>
+      <c r="D75" s="50"/>
+      <c r="E75" s="50"/>
       <c r="F75" s="34" t="s">
         <v>14</v>
       </c>
@@ -4739,13 +4752,13 @@
       <c r="AL76" s="20"/>
     </row>
     <row r="77" spans="1:38" ht="12" customHeight="1">
-      <c r="A77" s="51">
+      <c r="A77" s="49">
         <v>1</v>
       </c>
-      <c r="B77" s="48"/>
-      <c r="C77" s="48"/>
-      <c r="D77" s="48"/>
-      <c r="E77" s="48"/>
+      <c r="B77" s="51"/>
+      <c r="C77" s="51"/>
+      <c r="D77" s="51"/>
+      <c r="E77" s="51"/>
       <c r="F77" s="21" t="s">
         <v>13</v>
       </c>
@@ -4783,11 +4796,11 @@
       <c r="AL77" s="26"/>
     </row>
     <row r="78" spans="1:38" ht="12" customHeight="1">
-      <c r="A78" s="49"/>
-      <c r="B78" s="49"/>
-      <c r="C78" s="49"/>
-      <c r="D78" s="49"/>
-      <c r="E78" s="49"/>
+      <c r="A78" s="50"/>
+      <c r="B78" s="50"/>
+      <c r="C78" s="50"/>
+      <c r="D78" s="50"/>
+      <c r="E78" s="50"/>
       <c r="F78" s="27" t="s">
         <v>14</v>
       </c>
@@ -4825,13 +4838,13 @@
       <c r="AL78" s="30"/>
     </row>
     <row r="79" spans="1:38" ht="12" customHeight="1">
-      <c r="A79" s="51">
+      <c r="A79" s="49">
         <v>2</v>
       </c>
-      <c r="B79" s="48"/>
-      <c r="C79" s="48"/>
-      <c r="D79" s="48"/>
-      <c r="E79" s="48"/>
+      <c r="B79" s="51"/>
+      <c r="C79" s="51"/>
+      <c r="D79" s="51"/>
+      <c r="E79" s="51"/>
       <c r="F79" s="31" t="s">
         <v>13</v>
       </c>
@@ -4869,11 +4882,11 @@
       <c r="AL79" s="10"/>
     </row>
     <row r="80" spans="1:38" ht="12" customHeight="1">
-      <c r="A80" s="49"/>
-      <c r="B80" s="49"/>
-      <c r="C80" s="49"/>
-      <c r="D80" s="49"/>
-      <c r="E80" s="49"/>
+      <c r="A80" s="50"/>
+      <c r="B80" s="50"/>
+      <c r="C80" s="50"/>
+      <c r="D80" s="50"/>
+      <c r="E80" s="50"/>
       <c r="F80" s="34" t="s">
         <v>14</v>
       </c>
@@ -4911,13 +4924,13 @@
       <c r="AL80" s="37"/>
     </row>
     <row r="81" spans="1:38" ht="12" customHeight="1">
-      <c r="A81" s="51">
+      <c r="A81" s="49">
         <v>3</v>
       </c>
-      <c r="B81" s="48"/>
-      <c r="C81" s="48"/>
-      <c r="D81" s="48"/>
-      <c r="E81" s="48"/>
+      <c r="B81" s="51"/>
+      <c r="C81" s="51"/>
+      <c r="D81" s="51"/>
+      <c r="E81" s="51"/>
       <c r="F81" s="21" t="s">
         <v>13</v>
       </c>
@@ -4955,11 +4968,11 @@
       <c r="AL81" s="26"/>
     </row>
     <row r="82" spans="1:38" ht="12" customHeight="1">
-      <c r="A82" s="49"/>
-      <c r="B82" s="49"/>
-      <c r="C82" s="49"/>
-      <c r="D82" s="49"/>
-      <c r="E82" s="49"/>
+      <c r="A82" s="50"/>
+      <c r="B82" s="50"/>
+      <c r="C82" s="50"/>
+      <c r="D82" s="50"/>
+      <c r="E82" s="50"/>
       <c r="F82" s="38" t="s">
         <v>14</v>
       </c>
@@ -4997,13 +5010,13 @@
       <c r="AL82" s="30"/>
     </row>
     <row r="83" spans="1:38" ht="12" customHeight="1">
-      <c r="A83" s="51">
+      <c r="A83" s="49">
         <v>4</v>
       </c>
-      <c r="B83" s="48"/>
-      <c r="C83" s="48"/>
-      <c r="D83" s="48"/>
-      <c r="E83" s="48"/>
+      <c r="B83" s="51"/>
+      <c r="C83" s="51"/>
+      <c r="D83" s="51"/>
+      <c r="E83" s="51"/>
       <c r="F83" s="31" t="s">
         <v>13</v>
       </c>
@@ -5041,11 +5054,11 @@
       <c r="AL83" s="10"/>
     </row>
     <row r="84" spans="1:38" ht="12" customHeight="1">
-      <c r="A84" s="49"/>
-      <c r="B84" s="49"/>
-      <c r="C84" s="49"/>
-      <c r="D84" s="49"/>
-      <c r="E84" s="49"/>
+      <c r="A84" s="50"/>
+      <c r="B84" s="50"/>
+      <c r="C84" s="50"/>
+      <c r="D84" s="50"/>
+      <c r="E84" s="50"/>
       <c r="F84" s="38" t="s">
         <v>14</v>
       </c>
@@ -41724,16 +41737,174 @@
     </row>
   </sheetData>
   <mergeCells count="201">
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="E46:E47"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="D48:D49"/>
-    <mergeCell ref="E48:E49"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="C57:C58"/>
+    <mergeCell ref="D57:D58"/>
+    <mergeCell ref="E57:E58"/>
+    <mergeCell ref="A59:A60"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="D66:D67"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="D64:D65"/>
+    <mergeCell ref="E64:E65"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="E66:E67"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="D55:D56"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="C53:C54"/>
+    <mergeCell ref="D53:D54"/>
+    <mergeCell ref="E53:E54"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="E55:E56"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="E42:E43"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="E44:E45"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="D4:D6"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="O5:P5"/>
+    <mergeCell ref="Q5:R5"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="S5:T5"/>
+    <mergeCell ref="U5:V5"/>
+    <mergeCell ref="W5:X5"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="F4:F6"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G3:AL4"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="O6:P6"/>
+    <mergeCell ref="Q6:R6"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="U6:V6"/>
+    <mergeCell ref="W6:X6"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="E33:E34"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="E35:E36"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="B42:B43"/>
     <mergeCell ref="B46:B47"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="A77:A78"/>
+    <mergeCell ref="B77:B78"/>
+    <mergeCell ref="C77:C78"/>
+    <mergeCell ref="D77:D78"/>
+    <mergeCell ref="E77:E78"/>
+    <mergeCell ref="C81:C82"/>
+    <mergeCell ref="D81:D82"/>
+    <mergeCell ref="A81:A82"/>
+    <mergeCell ref="A83:A84"/>
+    <mergeCell ref="B83:B84"/>
+    <mergeCell ref="C83:C84"/>
+    <mergeCell ref="D83:D84"/>
+    <mergeCell ref="E83:E84"/>
+    <mergeCell ref="A79:A80"/>
+    <mergeCell ref="B79:B80"/>
+    <mergeCell ref="C79:C80"/>
+    <mergeCell ref="D79:D80"/>
+    <mergeCell ref="E79:E80"/>
+    <mergeCell ref="B81:B82"/>
+    <mergeCell ref="E81:E82"/>
+    <mergeCell ref="D74:D75"/>
+    <mergeCell ref="E74:E75"/>
+    <mergeCell ref="A70:A71"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="E72:E73"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="C74:C75"/>
     <mergeCell ref="A51:A52"/>
     <mergeCell ref="B51:B52"/>
     <mergeCell ref="C51:C52"/>
@@ -41758,173 +41929,15 @@
     <mergeCell ref="D59:D60"/>
     <mergeCell ref="E59:E60"/>
     <mergeCell ref="A57:A58"/>
-    <mergeCell ref="D74:D75"/>
-    <mergeCell ref="E74:E75"/>
-    <mergeCell ref="A70:A71"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="D72:D73"/>
-    <mergeCell ref="E72:E73"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="C74:C75"/>
-    <mergeCell ref="A77:A78"/>
-    <mergeCell ref="B77:B78"/>
-    <mergeCell ref="C77:C78"/>
-    <mergeCell ref="D77:D78"/>
-    <mergeCell ref="E77:E78"/>
-    <mergeCell ref="C81:C82"/>
-    <mergeCell ref="D81:D82"/>
-    <mergeCell ref="A81:A82"/>
-    <mergeCell ref="A83:A84"/>
-    <mergeCell ref="B83:B84"/>
-    <mergeCell ref="C83:C84"/>
-    <mergeCell ref="D83:D84"/>
-    <mergeCell ref="E83:E84"/>
-    <mergeCell ref="A79:A80"/>
-    <mergeCell ref="B79:B80"/>
-    <mergeCell ref="C79:C80"/>
-    <mergeCell ref="D79:D80"/>
-    <mergeCell ref="E79:E80"/>
-    <mergeCell ref="B81:B82"/>
-    <mergeCell ref="E81:E82"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="E33:E34"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="E35:E36"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="S5:T5"/>
-    <mergeCell ref="U5:V5"/>
-    <mergeCell ref="W5:X5"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="F4:F6"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G3:AL4"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="O6:P6"/>
-    <mergeCell ref="Q6:R6"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="U6:V6"/>
-    <mergeCell ref="W6:X6"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="B3:B6"/>
-    <mergeCell ref="C4:C6"/>
-    <mergeCell ref="D4:D6"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="O5:P5"/>
-    <mergeCell ref="Q5:R5"/>
-    <mergeCell ref="E4:E6"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="E27:E28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="E31:E32"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="D55:D56"/>
-    <mergeCell ref="A53:A54"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="C53:C54"/>
-    <mergeCell ref="D53:D54"/>
-    <mergeCell ref="E53:E54"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="E55:E56"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="E40:E41"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="E42:E43"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="E44:E45"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="B57:B58"/>
-    <mergeCell ref="C57:C58"/>
-    <mergeCell ref="D57:D58"/>
-    <mergeCell ref="E57:E58"/>
-    <mergeCell ref="A59:A60"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="D66:D67"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="C64:C65"/>
-    <mergeCell ref="D64:D65"/>
-    <mergeCell ref="E64:E65"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="E66:E67"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="E46:E47"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="E48:E49"/>
   </mergeCells>
   <phoneticPr fontId="7"/>
   <dataValidations count="1">
